--- a/Gastos/2026-08-Codiagro P&L para proyectar Sep.xlsx
+++ b/Gastos/2026-08-Codiagro P&L para proyectar Sep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroquimicacodiagro365-my.sharepoint.com/personal/oscar_ocampo_codiagro_com/Documents/Escritorio/Presupuesto 2026/Calsif Comerciales/Gastos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{684F3CC1-BFEB-4F21-8D99-3D56A49536AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{684F3CC1-BFEB-4F21-8D99-3D56A49536AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82563A28-2021-4113-93E7-94CE441A38D2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="804" activeTab="1" xr2:uid="{DA978C05-6AA7-4636-9B27-353885F16E02}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="804" activeTab="1" xr2:uid="{DA978C05-6AA7-4636-9B27-353885F16E02}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="24" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="PL Mensual 2026" sheetId="12" r:id="rId3"/>
     <sheet name="Ginger" sheetId="21" state="hidden" r:id="rId4"/>
     <sheet name="Extraitems 2026" sheetId="6" state="hidden" r:id="rId5"/>
-    <sheet name="Ext Items 2026" sheetId="14" r:id="rId6"/>
-    <sheet name="Ext Items Budget" sheetId="15" r:id="rId7"/>
-    <sheet name="Ext Items 2025" sheetId="16" r:id="rId8"/>
-    <sheet name="Cuenta Ok" sheetId="19" r:id="rId9"/>
+    <sheet name="Ext Items 2026" sheetId="14" state="hidden" r:id="rId6"/>
+    <sheet name="Ext Items Budget" sheetId="15" state="hidden" r:id="rId7"/>
+    <sheet name="Ext Items 2025" sheetId="16" state="hidden" r:id="rId8"/>
+    <sheet name="Cuenta Ok" sheetId="19" state="hidden" r:id="rId9"/>
     <sheet name="P&amp;L Mensualitzada 2025" sheetId="8" r:id="rId10"/>
     <sheet name="Budget26 sin EI" sheetId="7" r:id="rId11"/>
   </sheets>
@@ -36,9 +36,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
-    <pivotCache cacheId="1" r:id="rId13"/>
-    <pivotCache cacheId="2" r:id="rId14"/>
+    <pivotCache cacheId="17" r:id="rId12"/>
+    <pivotCache cacheId="18" r:id="rId13"/>
+    <pivotCache cacheId="24" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4035" uniqueCount="505">
   <si>
     <t>EUR</t>
   </si>
@@ -1406,36 +1406,21 @@
     <t>Coste semi-variable de consumibles de marcaje y codificación en planta vinculado al volumen de producción envasado.</t>
   </si>
   <si>
-    <t>Coste variable: subcontratación y apoyos externos de formulación según picos de carga fabril.</t>
-  </si>
-  <si>
     <t>Coste estratégico de I+D: ensayos agronómicos de eficacia y desarrollo de bioestimulantes.</t>
   </si>
   <si>
     <t>Coste fijo mensual según contratos vigentes de renting de vehículos y maquinaria auxiliar.</t>
   </si>
   <si>
-    <t>Coste fijo contractual: cuota mensual inalterada según contrato de arrendamiento Murano.</t>
-  </si>
-  <si>
-    <t>Coste semi-variable: mantenimiento preventivo y correctivo de planta ajustado por inflación (+4,5%).</t>
-  </si>
-  <si>
     <t>Coste fijo de asesoramiento legal, técnico y fiscal, con refuerzo en diciembre por preparación del cierre y auditoría.</t>
   </si>
   <si>
-    <t>Coste fijo mensual por servicios externos de gestión contable, fiscal y laboral.</t>
-  </si>
-  <si>
     <t>Gastos de registro de formulaciones, marcas y actos notariales.</t>
   </si>
   <si>
     <t>Proyección basada en el promedio mensual histórico de actividad.</t>
   </si>
   <si>
-    <t>Coste 100% variable: transporte nacional calculado en función del volumen de expediciones presupuestadas + incremento tarifas logísticas.</t>
-  </si>
-  <si>
     <t>Coste variable: transporte marítimo y terrestre de exportación según volumen internacional presupuestado + fletes internacionales.</t>
   </si>
   <si>
@@ -1484,18 +1469,6 @@
     <t>Coste fijo estricto: dotación lineal mensual calculada según las tablas oficiales de amortización y vida útil del inmovilizado.</t>
   </si>
   <si>
-    <t>Coste financiero por descuento comercial y confirming de proveedores vinculado al volumen de compras.</t>
-  </si>
-  <si>
-    <t>Proyección basada en el promedio mensual histórico.</t>
-  </si>
-  <si>
-    <t>Estimación conservadora basada en liquidaciones de divisas en exportación a tipos de cambio de mercado.</t>
-  </si>
-  <si>
-    <t>Rendimientos financieros por saldos de tesorería y cuentas remuneradas a cierre de año.</t>
-  </si>
-  <si>
     <t xml:space="preserve">sep-26 </t>
   </si>
   <si>
@@ -1511,18 +1484,6 @@
     <t>Provisión por rappels comerciales ajustada para alcanzar el objetivo anual exacto de 333.000,00 € (-148.761,28 € reales Ene-Ago + -184.238,72 € provisión Dic).</t>
   </si>
   <si>
-    <t>Coste variable directo: volumen de unidades a producir/vender según presupuesto ajustado (ratio histórico 27,0% s/ventas) + ajuste inflacionario de materias primas (+4,5%).</t>
-  </si>
-  <si>
-    <t>Coste variable por unidades envasadas (garrafas, bidones, IBCs): ratio histórico del 5,22% s/ventas ajustadas + incremento de precios de envases (+4,5% inflación).</t>
-  </si>
-  <si>
-    <t>Coste variable según volumen de unidades a etiquetar (0,57% s/ventas ajustadas) con ajuste de precios de imprenta.</t>
-  </si>
-  <si>
-    <t>Coste variable según expediciones y paletización requerida (0,59% s/ventas ajustadas) + inflación de suministros logísticos.</t>
-  </si>
-  <si>
     <t>Coste variable directamente proporcional al número de unidades/tapones envasados (0,22% s/ventas ajustadas).</t>
   </si>
   <si>
@@ -1541,19 +1502,79 @@
     <t xml:space="preserve">dic-26 </t>
   </si>
   <si>
-    <t>Honorarios y gastos comerciales de zona según plan presupuestado + 5.000,00 € adicionales en diciembre según instrucción comercial.</t>
-  </si>
-  <si>
-    <t>Dotación mensual de 500,00 € de sep a dic + 30.000,00 € extraordinarios en diciembre según instrucción comercial.</t>
-  </si>
-  <si>
-    <t>Dotación mensual de 6.000,00 € de sep a dic + 100.000,00 € extraordinarios en diciembre según instrucción comercial.</t>
-  </si>
-  <si>
     <t>Sin dotación presupuestada para el periodo sep-dic según instrucción comercial.</t>
   </si>
   <si>
     <t>Gastos de registro y mantenimiento de marca en El Salvador (única partida de marcas presupuestada en el periodo).</t>
+  </si>
+  <si>
+    <t>Coste variable directo: volumen según presupuesto ajustado (ratio histórico 25,85% s/ventas sin incremento de inflación en 2026; la inflación del +4,5% se aplica solo en 2027).</t>
+  </si>
+  <si>
+    <t>Coste variable por envases y embalajes: incluye saldo de junio traspasado de la 602000000 (-30.306,17 €). Estimación unificada según ratio histórico 5,39% s/ventas ajustadas (sin inflación en 2026; aplicable en 2027).</t>
+  </si>
+  <si>
+    <t>Cuenta fusionada con 602000001. Su saldo real de junio (-30.306,17 €) se ha traspasado a la 602000001. Sin previsión en sep-dic ni en 2027.</t>
+  </si>
+  <si>
+    <t>Coste variable de etiquetas: ratio s/ventas ajustadas sin ajuste de precios de imprenta por inflación en 2026 (solo en 2027).</t>
+  </si>
+  <si>
+    <t>Coste variable de palets: ratio s/ventas ajustadas sin inflación de suministros logísticos en 2026 (aplicable en 2027).</t>
+  </si>
+  <si>
+    <t>Coste variable de subcontratación fabril: eliminadas previsiones de sep a nov, dejando únicamente diciembre (-7.970,00 €) por refuerzo a cierre de ejercicio según indicación.</t>
+  </si>
+  <si>
+    <t>Arrendamiento Murano: no hay más cuotas en 2026 (ya está todo pagado, eliminadas sep-dic). En 2027 poner la misma cantidad anual ajustada a la inflación (+4,5%).</t>
+  </si>
+  <si>
+    <t>Coste semi-variable: mantenimiento preventivo y correctivo de planta según promedio mensual histórico (sin incremento de inflación en 2026; la inflación del +4,5% se aplica solo en 2027).</t>
+  </si>
+  <si>
+    <t>Servicios contables y financieros externos: restablecido a -2.800,00 €/mes en 2026 según indicación. La reducción del 50% (-1.400,00 €/mes) se aplica únicamente en el ejercicio 2027.</t>
+  </si>
+  <si>
+    <t>Honorarios y gastos comerciales de zona según plan presupuestado + 5.000,00 € adicionales en diciembre según instrucción comercial. Para 2027 no hay que subirles nada (mismo importe).</t>
+  </si>
+  <si>
+    <t>Dotación mensual de 500,00 € de sep a dic + 30.000,00 € extraordinarios en diciembre según instrucción comercial. Para 2027 no hay que subirles nada (mismo importe).</t>
+  </si>
+  <si>
+    <t>Dotación mensual de 6.000,00 € de sep a dic + 100.000,00 € extraordinarios en diciembre según instrucción comercial. Para 2027 no hay que subirles nada (mismo importe).</t>
+  </si>
+  <si>
+    <t>Comisiones Kamal Kehal: eliminados los importes de sep a dic del 2026. Para 2027 poner la misma cantidad anual real del 2026 (-3.398,55 €).</t>
+  </si>
+  <si>
+    <t>Coste variable de transporte nacional: mantenida temporalmente la previsión según volumen de expediciones presupuestadas; pendiente de recibir excel con previsiones logísticas.</t>
+  </si>
+  <si>
+    <t>Gastos de marketing: eliminadas las partidas de sep a dic del 2026. Para 2027 pendiente de adjuntar el plan de marketing.</t>
+  </si>
+  <si>
+    <t>Tasas: eliminados los importes previstos de sep a dic en 2026 por estar ya devengadas en mayo (-581,49 €). Para 2027 se replica exactamente el mismo gasto en mayo.</t>
+  </si>
+  <si>
+    <t>Tasas e impuestos municipales (IBI): eliminadas las partidas de sep a dic del 2026 por estar ya pagado en el ejercicio. En el 2027 poner la misma cantidad que ya se ha pagado en el 2026 (-7.396,59 €).</t>
+  </si>
+  <si>
+    <t>Ajustes negativos de IVA circulante: no van a tener más saldo; fijado a 0 de sep a dic 2026 y a 0 en 2027.</t>
+  </si>
+  <si>
+    <t>Pérdidas por deterioro de créditos: no van a tener más saldo; fijado a 0 de sep a dic 2026 y a 0 en 2027.</t>
+  </si>
+  <si>
+    <t>Intereses pago financiado proveedores: operación puntual en 2026; sin saldo de sep a dic 2026 ni en 2027.</t>
+  </si>
+  <si>
+    <t>Intereses préstamo Caixabank: préstamo ya finalizado; saldos fijados a 0 de sep a dic 2026 y a 0 en 2027.</t>
+  </si>
+  <si>
+    <t>Diferencias positivas de cambio: sin saldos estimados de sep a dic 2026 ni en 2027 según indicación.</t>
+  </si>
+  <si>
+    <t>Otros ingresos financieros: partida no recurrente de junio; sin saldos estimados de sep a dic 2026 ni en 2027.</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2517,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2984,13 +3005,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="73">
     <cellStyle name="20% - Énfasis1 2" xfId="35" xr:uid="{1185DB90-4849-424E-B2AB-58A2E7F5B16C}"/>
@@ -3294,7 +3320,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Oscar Ocampo" refreshedDate="46289.567853125001" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="202" xr:uid="{7D240FD3-DF79-461F-8DA4-41A4468E62DE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Oscar Ocampo" refreshedDate="46290.519526388889" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="202" xr:uid="{7D240FD3-DF79-461F-8DA4-41A4468E62DE}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B3:W205" sheet="PL Mensual 2026"/>
   </cacheSource>
@@ -3366,19 +3392,19 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-189242.44" maxValue="802410.56"/>
     </cacheField>
     <cacheField name="sep-26" numFmtId="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-129824.18" maxValue="480563.3"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-128060.74" maxValue="480563.3"/>
     </cacheField>
     <cacheField name="oct-26" numFmtId="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-245926.61" maxValue="910333.55"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-235336.47" maxValue="910333.55"/>
     </cacheField>
     <cacheField name="nov-26" numFmtId="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-330610.32" maxValue="1223802.77"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-316373.51" maxValue="1223802.77"/>
     </cacheField>
     <cacheField name="dic-26" numFmtId="4">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-407060.74" maxValue="1321267.54"/>
     </cacheField>
     <cacheField name="Total 2026" numFmtId="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-4111061.0299999993" maxValue="15420283.770000003"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-4065272.9299999997" maxValue="15420283.770000003"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -4603,11 +4629,11 @@
     <n v="-393937.01"/>
     <n v="-362186.44"/>
     <n v="-189242.44"/>
-    <n v="-129824.18"/>
-    <n v="-245926.61"/>
-    <n v="-330610.32"/>
-    <n v="-356940.43"/>
-    <n v="-4111061.0299999993"/>
+    <n v="-124233.67"/>
+    <n v="-235336.47"/>
+    <n v="-316373.51"/>
+    <n v="-341569.79"/>
+    <n v="-4065272.9299999997"/>
   </r>
   <r>
     <x v="0"/>
@@ -4624,14 +4650,14 @@
     <n v="-55812.27"/>
     <n v="-92652.34"/>
     <n v="-30193.149999999991"/>
-    <n v="-89165.98000000001"/>
+    <n v="-119472.15"/>
     <n v="-145291.04999999999"/>
     <n v="-8606.0399999999936"/>
-    <n v="-25070.99"/>
-    <n v="-47492.1"/>
-    <n v="-63845.79"/>
-    <n v="-68930.53"/>
-    <n v="-793861.58"/>
+    <n v="-25894.98"/>
+    <n v="-49053"/>
+    <n v="-65944.179999999993"/>
+    <n v="-71196.03"/>
+    <n v="-830916.5299999998"/>
   </r>
   <r>
     <x v="0"/>
@@ -4648,14 +4674,14 @@
     <m/>
     <m/>
     <m/>
-    <n v="-30306.17"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="-30306.17"/>
-    <n v="-30306.17"/>
-    <n v="-30306.17"/>
-    <n v="-30306.17"/>
-    <n v="-151530.84999999998"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="0"/>
@@ -4675,11 +4701,11 @@
     <n v="-5867.49"/>
     <n v="-10270.19"/>
     <n v="-2886.68"/>
-    <n v="-2744.02"/>
-    <n v="-5198"/>
-    <n v="-6987.91"/>
-    <n v="-7544.44"/>
-    <n v="-86934.27"/>
+    <n v="-2625.86"/>
+    <n v="-4974.16"/>
+    <n v="-6687"/>
+    <n v="-7219.56"/>
+    <n v="-85966.48"/>
   </r>
   <r>
     <x v="0"/>
@@ -4699,11 +4725,11 @@
     <n v="-12994.8"/>
     <n v="-4331.6000000000004"/>
     <n v="-4331.6000000000004"/>
-    <n v="-2854.55"/>
-    <n v="-5407.38"/>
-    <n v="-7269.39"/>
-    <n v="-7848.33"/>
-    <n v="-90442.1"/>
+    <n v="-2731.63"/>
+    <n v="-5174.53"/>
+    <n v="-6956.35"/>
+    <n v="-7510.36"/>
+    <n v="-89435.32"/>
   </r>
   <r>
     <x v="0"/>
@@ -4963,11 +4989,11 @@
     <n v="0.72000000000116415"/>
     <n v="-3900"/>
     <n v="-6131.3100000000013"/>
-    <n v="-5480"/>
-    <n v="-6480"/>
-    <n v="-7470"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
     <n v="-7970"/>
-    <n v="-85188.09"/>
+    <n v="-65758.09"/>
   </r>
   <r>
     <x v="0"/>
@@ -5539,11 +5565,11 @@
     <s v="                            -  "/>
     <n v="-6139.04"/>
     <n v="0"/>
-    <n v="-2695.12"/>
-    <n v="-2695.12"/>
-    <n v="-2695.12"/>
-    <n v="-2695.12"/>
-    <n v="-32341.439999999995"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-21560.959999999999"/>
   </r>
   <r>
     <x v="0"/>
@@ -6043,11 +6069,11 @@
     <n v="-790.66"/>
     <s v="                                             -  "/>
     <n v="0"/>
-    <n v="-748.65"/>
-    <n v="-748.65"/>
-    <n v="-748.65"/>
-    <n v="-748.65"/>
-    <n v="-6576.6799999999985"/>
+    <n v="-716.42"/>
+    <n v="-716.42"/>
+    <n v="-716.42"/>
+    <n v="-716.42"/>
+    <n v="-6447.76"/>
   </r>
   <r>
     <x v="0"/>
@@ -6067,11 +6093,11 @@
     <n v="-979.23"/>
     <s v="                                             -  "/>
     <n v="-115.48"/>
-    <n v="-731.87"/>
-    <n v="-731.87"/>
-    <n v="-731.87"/>
-    <n v="-731.87"/>
-    <n v="-5028.55"/>
+    <n v="-700.36"/>
+    <n v="-700.36"/>
+    <n v="-700.36"/>
+    <n v="-700.36"/>
+    <n v="-4902.51"/>
   </r>
   <r>
     <x v="0"/>
@@ -6091,11 +6117,11 @@
     <s v="                            -  "/>
     <n v="-196.99"/>
     <n v="0"/>
-    <n v="-122.19"/>
-    <n v="-122.19"/>
-    <n v="-122.19"/>
-    <n v="-122.19"/>
-    <n v="-956.46"/>
+    <n v="-116.92"/>
+    <n v="-116.92"/>
+    <n v="-116.92"/>
+    <n v="-116.92"/>
+    <n v="-935.37999999999988"/>
   </r>
   <r>
     <x v="0"/>
@@ -6115,11 +6141,11 @@
     <n v="-1900.59"/>
     <n v="-2274.92"/>
     <n v="0"/>
-    <n v="-1425.85"/>
-    <n v="-1425.85"/>
-    <n v="-1425.85"/>
-    <n v="-1425.85"/>
-    <n v="-12525.640000000001"/>
+    <n v="-1364.45"/>
+    <n v="-1364.45"/>
+    <n v="-1364.45"/>
+    <n v="-1364.45"/>
+    <n v="-12280.04"/>
   </r>
   <r>
     <x v="0"/>
@@ -6139,11 +6165,11 @@
     <s v="                            -  "/>
     <n v="0"/>
     <n v="0"/>
-    <n v="-249.63"/>
-    <n v="-249.63"/>
-    <n v="-249.63"/>
-    <n v="-249.63"/>
-    <n v="-1237.4000000000001"/>
+    <n v="-238.88"/>
+    <n v="-238.88"/>
+    <n v="-238.88"/>
+    <n v="-238.88"/>
+    <n v="-1194.4000000000001"/>
   </r>
   <r>
     <x v="0"/>
@@ -6163,11 +6189,11 @@
     <s v="                            -  "/>
     <n v="-634.91"/>
     <n v="0"/>
-    <n v="-515.01"/>
-    <n v="-515.01"/>
-    <n v="-515.01"/>
-    <n v="-515.01"/>
-    <n v="-3045.7"/>
+    <n v="-492.83"/>
+    <n v="-492.83"/>
+    <n v="-492.83"/>
+    <n v="-492.83"/>
+    <n v="-2956.98"/>
   </r>
   <r>
     <x v="0"/>
@@ -6211,11 +6237,11 @@
     <n v="-1566.9"/>
     <n v="-642.6"/>
     <n v="-977.98"/>
-    <n v="-935.11"/>
-    <n v="-935.11"/>
-    <n v="-935.11"/>
-    <n v="-935.11"/>
-    <n v="-9109.5199999999986"/>
+    <n v="-894.85"/>
+    <n v="-894.85"/>
+    <n v="-894.85"/>
+    <n v="-894.85"/>
+    <n v="-8948.4800000000014"/>
   </r>
   <r>
     <x v="0"/>
@@ -6235,11 +6261,11 @@
     <n v="0"/>
     <n v="-1409.04"/>
     <n v="0"/>
-    <n v="-1472.45"/>
-    <n v="-1472.45"/>
-    <n v="-1472.45"/>
-    <n v="-1472.45"/>
-    <n v="-7298.8399999999992"/>
+    <n v="-1409.04"/>
+    <n v="-1409.04"/>
+    <n v="-1409.04"/>
+    <n v="-1409.04"/>
+    <n v="-7045.2"/>
   </r>
   <r>
     <x v="0"/>
@@ -6283,11 +6309,11 @@
     <n v="-354.5"/>
     <n v="-9441.85"/>
     <n v="-1983.69"/>
-    <n v="-2527.63"/>
-    <n v="-2527.63"/>
-    <n v="-2527.63"/>
-    <n v="-2527.63"/>
-    <n v="-27041.980000000003"/>
+    <n v="-2418.7800000000002"/>
+    <n v="-2418.7800000000002"/>
+    <n v="-2418.7800000000002"/>
+    <n v="-2418.7800000000002"/>
+    <n v="-26606.579999999994"/>
   </r>
   <r>
     <x v="0"/>
@@ -6307,11 +6333,11 @@
     <n v="-4282.05"/>
     <n v="-5230"/>
     <n v="-5848.16"/>
-    <n v="-4187.1400000000003"/>
-    <n v="-4187.1400000000003"/>
-    <n v="-4187.1400000000003"/>
-    <n v="-4187.1400000000003"/>
-    <n v="-32775.89"/>
+    <n v="-4006.83"/>
+    <n v="-4006.83"/>
+    <n v="-4006.83"/>
+    <n v="-4006.83"/>
+    <n v="-32054.65"/>
   </r>
   <r>
     <x v="0"/>
@@ -6331,11 +6357,11 @@
     <n v="-4467.0200000000004"/>
     <s v="                                             -  "/>
     <n v="-11965.55"/>
-    <n v="-5939.08"/>
-    <n v="-5939.08"/>
-    <n v="-5939.08"/>
-    <n v="-5939.08"/>
-    <n v="-40806.310000000005"/>
+    <n v="-5683.33"/>
+    <n v="-5683.33"/>
+    <n v="-5683.33"/>
+    <n v="-5683.33"/>
+    <n v="-39783.310000000005"/>
   </r>
   <r>
     <x v="0"/>
@@ -6355,11 +6381,11 @@
     <n v="-8017.35"/>
     <n v="5697.8"/>
     <n v="-288.39"/>
-    <n v="-915.9"/>
-    <n v="-915.9"/>
-    <n v="-915.9"/>
-    <n v="-915.9"/>
-    <n v="-8922.3499999999985"/>
+    <n v="-876.46"/>
+    <n v="-876.46"/>
+    <n v="-876.46"/>
+    <n v="-876.46"/>
+    <n v="-8764.59"/>
   </r>
   <r>
     <x v="0"/>
@@ -6379,11 +6405,11 @@
     <n v="-106.8"/>
     <s v="                                             -  "/>
     <n v="-108.17"/>
-    <n v="-788.2"/>
-    <n v="-788.2"/>
-    <n v="-788.2"/>
-    <n v="-788.2"/>
-    <n v="-7678.37"/>
+    <n v="-754.26"/>
+    <n v="-754.26"/>
+    <n v="-754.26"/>
+    <n v="-754.26"/>
+    <n v="-7542.6100000000015"/>
   </r>
   <r>
     <x v="0"/>
@@ -6403,11 +6429,11 @@
     <n v="-81.8"/>
     <s v="                                             -  "/>
     <n v="0"/>
-    <n v="-121.44"/>
-    <n v="-121.44"/>
-    <n v="-121.44"/>
-    <n v="-121.44"/>
-    <n v="-834.40000000000009"/>
+    <n v="-116.21"/>
+    <n v="-116.21"/>
+    <n v="-116.21"/>
+    <n v="-116.21"/>
+    <n v="-813.48"/>
   </r>
   <r>
     <x v="0"/>
@@ -6619,11 +6645,11 @@
     <s v="                            -  "/>
     <n v="0"/>
     <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
     <n v="-3398.55"/>
-    <n v="-3398.55"/>
-    <n v="-3398.55"/>
-    <n v="-3398.55"/>
-    <n v="-16992.75"/>
   </r>
   <r>
     <x v="0"/>
@@ -7603,11 +7629,11 @@
     <n v="-3000"/>
     <s v="                                             -  "/>
     <n v="0"/>
-    <n v="-2277.14"/>
-    <n v="-3415.71"/>
-    <n v="-2277.14"/>
-    <n v="-2277.14"/>
-    <n v="-19355.71"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-9108.58"/>
   </r>
   <r>
     <x v="0"/>
@@ -8395,11 +8421,11 @@
     <s v="                            -  "/>
     <n v="0"/>
     <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
     <n v="-581.49"/>
-    <n v="-581.49"/>
-    <n v="-581.49"/>
-    <n v="-581.49"/>
-    <n v="-2907.45"/>
   </r>
   <r>
     <x v="0"/>
@@ -8419,11 +8445,11 @@
     <m/>
     <m/>
     <n v="-7396.59"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
     <n v="-7396.59"/>
-    <n v="-7396.59"/>
-    <n v="-7396.59"/>
-    <n v="-7396.59"/>
-    <n v="-36982.949999999997"/>
   </r>
   <r>
     <x v="0"/>
@@ -8467,11 +8493,11 @@
     <s v="                            -  "/>
     <n v="0"/>
     <n v="0"/>
-    <n v="-691.02"/>
-    <n v="-691.02"/>
-    <n v="-691.02"/>
-    <n v="-691.02"/>
-    <n v="-5528.16"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-2764.08"/>
   </r>
   <r>
     <x v="0"/>
@@ -8491,11 +8517,11 @@
     <n v="-211.6"/>
     <s v="                                             -  "/>
     <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
     <n v="-211.6"/>
-    <n v="-211.6"/>
-    <n v="-211.6"/>
-    <n v="-211.6"/>
-    <n v="-1058"/>
   </r>
   <r>
     <x v="0"/>
@@ -8708,10 +8734,10 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="-500"/>
-    <n v="-800"/>
-    <n v="-1000"/>
-    <n v="-3237.05"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-937.05"/>
   </r>
   <r>
     <x v="0"/>
@@ -8731,11 +8757,11 @@
     <n v="-8.86"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="-37.049999999999997"/>
-    <n v="-37.049999999999997"/>
-    <n v="-37.049999999999997"/>
-    <n v="-37.049999999999997"/>
-    <n v="-333.45000000000005"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-185.25"/>
   </r>
   <r>
     <x v="0"/>
@@ -8923,11 +8949,11 @@
     <n v="1665.7"/>
     <n v="604.76"/>
     <n v="0"/>
-    <n v="400"/>
-    <n v="600"/>
-    <n v="800"/>
-    <n v="800"/>
-    <n v="7844.51"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5244.51"/>
   </r>
   <r>
     <x v="0"/>
@@ -8974,14 +9000,14 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="2500"/>
-    <n v="6995.93"/>
+    <n v="0"/>
+    <n v="4495.93"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{20404466-1C8F-4694-BEC9-2336FD9092D9}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Detalle sin Ajustar">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{20404466-1C8F-4694-BEC9-2336FD9092D9}" name="TablaDinámica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Detalle sin Ajustar">
   <location ref="B3:O16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -9276,7 +9302,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{574F8F0F-CABA-44C9-861D-B64737513C38}" name="TablaDinámica13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{574F8F0F-CABA-44C9-861D-B64737513C38}" name="TablaDinámica13" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="P3:Q12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField numFmtId="14" showAll="0"/>
@@ -9373,7 +9399,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCFB44B8-C86C-4350-A9CC-CF0A10A66821}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCFB44B8-C86C-4350-A9CC-CF0A10A66821}" name="TablaDinámica2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:N33" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField numFmtId="14" showAll="0"/>
@@ -9804,7 +9830,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J31"/>
+  <dimension ref="A2:AS31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="70"/>
@@ -9818,7 +9844,7 @@
     <col min="10" max="16384" width="10.81640625" style="70"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" s="69"/>
       <c r="B2" s="104" t="s">
         <v>64</v>
@@ -9831,28 +9857,102 @@
       <c r="H2" s="129"/>
       <c r="I2" s="129"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="C4" s="103" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L4" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="71"/>
+      <c r="U4" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" s="71"/>
+      <c r="AD4" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE4" s="71"/>
+      <c r="AM4" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN4" s="71"/>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B5" s="72" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="73">
+        <v>9</v>
+      </c>
+      <c r="G5" s="68"/>
+      <c r="K5" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="73">
+        <v>10</v>
+      </c>
+      <c r="M5" s="71"/>
+      <c r="P5" s="68"/>
+      <c r="T5" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="U5" s="73">
+        <v>11</v>
+      </c>
+      <c r="V5" s="71"/>
+      <c r="Y5" s="68"/>
+      <c r="AC5" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD5" s="73">
         <v>12</v>
       </c>
-      <c r="G5" s="68"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="AE5" s="71"/>
+      <c r="AH5" s="68"/>
+      <c r="AL5" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM5" s="73">
+        <v>12</v>
+      </c>
+      <c r="AN5" s="71"/>
+      <c r="AQ5" s="68"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="71"/>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B7" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="70"/>
       <c r="D7" s="168"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K7" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="168"/>
+      <c r="T7" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="V7" s="168"/>
+      <c r="AC7" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE7" s="168"/>
+      <c r="AL7" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN7" s="168"/>
+    </row>
+    <row r="8" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="75"/>
       <c r="C8" s="76"/>
       <c r="D8" s="76"/>
@@ -9861,13 +9961,61 @@
       </c>
       <c r="F8" s="78"/>
       <c r="G8" s="79"/>
-      <c r="H8" s="170" t="s">
+      <c r="H8" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="170"/>
+      <c r="I8" s="169"/>
       <c r="J8" s="105"/>
-    </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K8" s="75"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="78"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="169" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="169"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" s="78"/>
+      <c r="Y8" s="79"/>
+      <c r="Z8" s="169" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA8" s="169"/>
+      <c r="AC8" s="75"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG8" s="78"/>
+      <c r="AH8" s="79"/>
+      <c r="AI8" s="169" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ8" s="169"/>
+      <c r="AL8" s="75"/>
+      <c r="AM8" s="76"/>
+      <c r="AN8" s="76"/>
+      <c r="AO8" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP8" s="78"/>
+      <c r="AQ8" s="79"/>
+      <c r="AR8" s="169" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS8" s="169"/>
+    </row>
+    <row r="9" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="80" t="s">
         <v>18</v>
       </c>
@@ -9893,8 +10041,104 @@
         <v>24</v>
       </c>
       <c r="J9" s="106"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K9" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="T9" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="V9" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="W9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="X9" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y9" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC9" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD9" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE9" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH9" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL9" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM9" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN9" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ9" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR9" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B10" s="83" t="s">
         <v>1</v>
       </c>
@@ -9903,32 +10147,156 @@
         <v>483.08373999999998</v>
       </c>
       <c r="D10" s="111">
-        <f>VLOOKUP(B10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>12778.049170000004</v>
+        <f>VLOOKUP(B10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>842.11579000000006</v>
       </c>
       <c r="E10" s="112">
         <f>C10-D10</f>
-        <v>-12294.965430000004</v>
+        <v>-359.03205000000008</v>
       </c>
       <c r="F10" s="127">
         <f>+IF(IFERROR(C10/D10-1,"-")&lt;300%,IFERROR(C10/D10-1,"-"),"n.a.")</f>
-        <v>-0.96219424940591303</v>
+        <v>-0.42634522979316192</v>
       </c>
       <c r="G10" s="120">
-        <f>VLOOKUP(B10,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
-        <v>15938.999998506453</v>
+        <f>VLOOKUP(B10,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
+        <v>1026.5684889409886</v>
       </c>
       <c r="H10" s="112">
         <f>C10-G10</f>
-        <v>-15455.916258506453</v>
+        <v>-543.48474894098854</v>
       </c>
       <c r="I10" s="127">
         <f>+IF(IFERROR(C10/G10-1,"-")&lt;300%,IFERROR(C10/G10-1,"-"),"n.a.")</f>
-        <v>-0.96969171591409331</v>
+        <v>-0.52941888904231726</v>
       </c>
       <c r="J10" s="107"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K10" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="111">
+        <f>(GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","1.- Importe neto de la cifra de negocios"))/1000</f>
+        <v>912.05501000000004</v>
+      </c>
+      <c r="M10" s="111">
+        <f>VLOOKUP(K10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>699.58345000000179</v>
+      </c>
+      <c r="N10" s="112">
+        <f>L10-M10</f>
+        <v>212.47155999999825</v>
+      </c>
+      <c r="O10" s="127">
+        <f>+IF(IFERROR(L10/M10-1,"-")&lt;300%,IFERROR(L10/M10-1,"-"),"n.a.")</f>
+        <v>0.3037115300540596</v>
+      </c>
+      <c r="P10" s="120">
+        <f>VLOOKUP(K10,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>798.567184017253</v>
+      </c>
+      <c r="Q10" s="112">
+        <f>L10-P10</f>
+        <v>113.48782598274704</v>
+      </c>
+      <c r="R10" s="127">
+        <f>+IF(IFERROR(L10/P10-1,"-")&lt;300%,IFERROR(L10/P10-1,"-"),"n.a.")</f>
+        <v>0.14211431205053771</v>
+      </c>
+      <c r="T10" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="111">
+        <f>(GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","1.- Importe neto de la cifra de negocios"))/1000</f>
+        <v>1225.32178</v>
+      </c>
+      <c r="V10" s="111">
+        <f>VLOOKUP(T10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>749.69916000000057</v>
+      </c>
+      <c r="W10" s="112">
+        <f>U10-V10</f>
+        <v>475.62261999999942</v>
+      </c>
+      <c r="X10" s="127">
+        <f>+IF(IFERROR(U10/V10-1,"-")&lt;300%,IFERROR(U10/V10-1,"-"),"n.a.")</f>
+        <v>0.63441797106988762</v>
+      </c>
+      <c r="Y10" s="120">
+        <f>VLOOKUP(T10,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>1030.2430087822902</v>
+      </c>
+      <c r="Z10" s="112">
+        <f>U10-Y10</f>
+        <v>195.0787712177098</v>
+      </c>
+      <c r="AA10" s="127">
+        <f>+IF(IFERROR(U10/Y10-1,"-")&lt;300%,IFERROR(U10/Y10-1,"-"),"n.a.")</f>
+        <v>0.18935219123523672</v>
+      </c>
+      <c r="AC10" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="111">
+        <f>(GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","1.- Importe neto de la cifra de negocios"))/1000</f>
+        <v>1142.4073800000001</v>
+      </c>
+      <c r="AE10" s="111">
+        <f>VLOOKUP(AC10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>248.50601</v>
+      </c>
+      <c r="AF10" s="112">
+        <f>AD10-AE10</f>
+        <v>893.90137000000004</v>
+      </c>
+      <c r="AG10" s="127" t="str">
+        <f>+IF(IFERROR(AD10/AE10-1,"-")&lt;300%,IFERROR(AD10/AE10-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AH10" s="120">
+        <f>VLOOKUP(AC10,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>659.94465275764242</v>
+      </c>
+      <c r="AI10" s="112">
+        <f>AD10-AH10</f>
+        <v>482.46272724235769</v>
+      </c>
+      <c r="AJ10" s="127">
+        <f>+IF(IFERROR(AD10/AH10-1,"-")&lt;300%,IFERROR(AD10/AH10-1,"-"),"n.a.")</f>
+        <v>0.7310654389369482</v>
+      </c>
+      <c r="AL10" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="111">
+        <f>(GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","1.- Importe neto de la cifra de negocios"))/1000</f>
+        <v>15180.000000000002</v>
+      </c>
+      <c r="AN10" s="111">
+        <f>VLOOKUP(AL10,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>248.50601</v>
+      </c>
+      <c r="AO10" s="112">
+        <f>AM10-AN10</f>
+        <v>14931.493990000003</v>
+      </c>
+      <c r="AP10" s="127" t="str">
+        <f>+IF(IFERROR(AM10/AN10-1,"-")&lt;300%,IFERROR(AM10/AN10-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ10" s="120">
+        <f>VLOOKUP(AL10,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>659.94465275764242</v>
+      </c>
+      <c r="AR10" s="112">
+        <f>AM10-AQ10</f>
+        <v>14520.05534724236</v>
+      </c>
+      <c r="AS10" s="127" t="str">
+        <f>+IF(IFERROR(AM10/AQ10-1,"-")&lt;300%,IFERROR(AM10/AQ10-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B11" s="75" t="s">
         <v>2</v>
       </c>
@@ -9936,32 +10304,156 @@
         <v>-80</v>
       </c>
       <c r="D11" s="113">
-        <f>VLOOKUP(B11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>-4286.3407700000007</v>
+        <f>VLOOKUP(B11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>-265.37090999999998</v>
       </c>
       <c r="E11" s="114">
         <f>C11-D11</f>
-        <v>4206.3407700000007</v>
+        <v>185.37090999999998</v>
       </c>
       <c r="F11" s="115">
         <f>+IF(IFERROR(C11/D11-1,"-")&lt;300%,IFERROR(C11/D11-1,"-"),"n.a.")</f>
-        <v>-0.98133606162162412</v>
+        <v>-0.69853515594456073</v>
       </c>
       <c r="G11" s="121">
-        <f>VLOOKUP(B11,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
-        <v>-5473.9999956159636</v>
+        <f>VLOOKUP(B11,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
+        <v>-352.55893085151547</v>
       </c>
       <c r="H11" s="114">
         <f>C11-G11</f>
-        <v>5393.9999956159636</v>
+        <v>272.55893085151547</v>
       </c>
       <c r="I11" s="115">
         <f t="shared" ref="I11:I29" si="0">+IF(IFERROR(C11/G11-1,"-")&lt;300%,IFERROR(C11/G11-1,"-"),"n.a.")</f>
-        <v>-0.98538545851953407</v>
+        <v>-0.77308758054495863</v>
       </c>
       <c r="J11" s="85"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K11" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="113">
+        <f>(GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","2.- Variación de existencias")+GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","4.- Aprovisionamientos"))/1000</f>
+        <v>-302.10136</v>
+      </c>
+      <c r="M11" s="113">
+        <f>VLOOKUP(K11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>-361.07370999999995</v>
+      </c>
+      <c r="N11" s="114">
+        <f>L11-M11</f>
+        <v>58.972349999999949</v>
+      </c>
+      <c r="O11" s="115">
+        <f>+IF(IFERROR(L11/M11-1,"-")&lt;300%,IFERROR(L11/M11-1,"-"),"n.a.")</f>
+        <v>-0.16332496209707414</v>
+      </c>
+      <c r="P11" s="121">
+        <f>VLOOKUP(K11,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>-274.25543998595526</v>
+      </c>
+      <c r="Q11" s="114">
+        <f>L11-P11</f>
+        <v>-27.845920014044736</v>
+      </c>
+      <c r="R11" s="115">
+        <f t="shared" ref="R11:R29" si="1">+IF(IFERROR(L11/P11-1,"-")&lt;300%,IFERROR(L11/P11-1,"-"),"n.a.")</f>
+        <v>0.10153279007144111</v>
+      </c>
+      <c r="T11" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="U11" s="113">
+        <f>(GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","2.- Variación de existencias")+GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","4.- Aprovisionamientos"))/1000</f>
+        <v>-404.42328000000003</v>
+      </c>
+      <c r="V11" s="113">
+        <f>VLOOKUP(T11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>-275.74654000000027</v>
+      </c>
+      <c r="W11" s="114">
+        <f>U11-V11</f>
+        <v>-128.67673999999977</v>
+      </c>
+      <c r="X11" s="115">
+        <f>+IF(IFERROR(U11/V11-1,"-")&lt;300%,IFERROR(U11/V11-1,"-"),"n.a.")</f>
+        <v>0.46664861143860459</v>
+      </c>
+      <c r="Y11" s="121">
+        <f>VLOOKUP(T11,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>-353.82088736060172</v>
+      </c>
+      <c r="Z11" s="114">
+        <f>U11-Y11</f>
+        <v>-50.602392639398317</v>
+      </c>
+      <c r="AA11" s="115">
+        <f t="shared" ref="AA11:AA29" si="2">+IF(IFERROR(U11/Y11-1,"-")&lt;300%,IFERROR(U11/Y11-1,"-"),"n.a.")</f>
+        <v>0.14301697397481838</v>
+      </c>
+      <c r="AC11" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="113">
+        <f>(GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","2.- Variación de existencias")+GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","4.- Aprovisionamientos"))/1000</f>
+        <v>-449.14532999999994</v>
+      </c>
+      <c r="AE11" s="113">
+        <f>VLOOKUP(AC11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-116.42869999999995</v>
+      </c>
+      <c r="AF11" s="114">
+        <f>AD11-AE11</f>
+        <v>-332.71663000000001</v>
+      </c>
+      <c r="AG11" s="115">
+        <f>+IF(IFERROR(AD11/AE11-1,"-")&lt;300%,IFERROR(AD11/AE11-1,"-"),"n.a.")</f>
+        <v>2.8576856908992383</v>
+      </c>
+      <c r="AH11" s="121">
+        <f>VLOOKUP(AC11,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-226.64682322769076</v>
+      </c>
+      <c r="AI11" s="114">
+        <f>AD11-AH11</f>
+        <v>-222.49850677230918</v>
+      </c>
+      <c r="AJ11" s="115">
+        <f t="shared" ref="AJ11:AJ29" si="3">+IF(IFERROR(AD11/AH11-1,"-")&lt;300%,IFERROR(AD11/AH11-1,"-"),"n.a.")</f>
+        <v>0.981697001544936</v>
+      </c>
+      <c r="AL11" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM11" s="113">
+        <f>(GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","2.- Variación de existencias")+GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","4.- Aprovisionamientos"))/1000</f>
+        <v>-5233.5328499999996</v>
+      </c>
+      <c r="AN11" s="113">
+        <f>VLOOKUP(AL11,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-116.42869999999995</v>
+      </c>
+      <c r="AO11" s="114">
+        <f>AM11-AN11</f>
+        <v>-5117.1041499999992</v>
+      </c>
+      <c r="AP11" s="115" t="str">
+        <f>+IF(IFERROR(AM11/AN11-1,"-")&lt;300%,IFERROR(AM11/AN11-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ11" s="121">
+        <f>VLOOKUP(AL11,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-226.64682322769076</v>
+      </c>
+      <c r="AR11" s="114">
+        <f>AM11-AQ11</f>
+        <v>-5006.8860267723085</v>
+      </c>
+      <c r="AS11" s="115" t="str">
+        <f t="shared" ref="AS11:AS29" si="4">+IF(IFERROR(AM11/AQ11-1,"-")&lt;300%,IFERROR(AM11/AQ11-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B12" s="86" t="s">
         <v>3</v>
       </c>
@@ -9971,31 +10463,155 @@
       </c>
       <c r="D12" s="25">
         <f>SUM(D10:D11)</f>
-        <v>8491.7084000000032</v>
+        <v>576.74488000000008</v>
       </c>
       <c r="E12" s="117">
-        <f t="shared" ref="E12" si="1">C12-D12</f>
-        <v>-8088.6246600000031</v>
+        <f t="shared" ref="E12" si="5">C12-D12</f>
+        <v>-173.6611400000001</v>
       </c>
       <c r="F12" s="118">
-        <f t="shared" ref="F12:F29" si="2">+IF(IFERROR(C12/D12-1,"-")&lt;300%,IFERROR(C12/D12-1,"-"),"n.a.")</f>
-        <v>-0.95253207941054596</v>
+        <f t="shared" ref="F12:F29" si="6">+IF(IFERROR(C12/D12-1,"-")&lt;300%,IFERROR(C12/D12-1,"-"),"n.a.")</f>
+        <v>-0.30110564657288341</v>
       </c>
       <c r="G12" s="117">
         <f>SUM(G10:G11)</f>
-        <v>10465.000002890491</v>
+        <v>674.0095580894731</v>
       </c>
       <c r="H12" s="117">
-        <f t="shared" ref="H12" si="3">C12-G12</f>
-        <v>-10061.916262890491</v>
+        <f t="shared" ref="H12" si="7">C12-G12</f>
+        <v>-270.92581808947313</v>
       </c>
       <c r="I12" s="118">
         <f t="shared" si="0"/>
-        <v>-0.96148268132932002</v>
+        <v>-0.40196138888212685</v>
       </c>
       <c r="J12" s="108"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K12" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="116">
+        <f>L10+L11</f>
+        <v>609.95365000000004</v>
+      </c>
+      <c r="M12" s="25">
+        <f>SUM(M10:M11)</f>
+        <v>338.50974000000184</v>
+      </c>
+      <c r="N12" s="117">
+        <f t="shared" ref="N12" si="8">L12-M12</f>
+        <v>271.4439099999982</v>
+      </c>
+      <c r="O12" s="118">
+        <f t="shared" ref="O12:O29" si="9">+IF(IFERROR(L12/M12-1,"-")&lt;300%,IFERROR(L12/M12-1,"-"),"n.a.")</f>
+        <v>0.80187917192573765</v>
+      </c>
+      <c r="P12" s="117">
+        <f>SUM(P10:P11)</f>
+        <v>524.31174403129774</v>
+      </c>
+      <c r="Q12" s="117">
+        <f t="shared" ref="Q12" si="10">L12-P12</f>
+        <v>85.641905968702304</v>
+      </c>
+      <c r="R12" s="118">
+        <f t="shared" si="1"/>
+        <v>0.16334157482383249</v>
+      </c>
+      <c r="T12" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="116">
+        <f>U10+U11</f>
+        <v>820.89850000000001</v>
+      </c>
+      <c r="V12" s="25">
+        <f>SUM(V10:V11)</f>
+        <v>473.95262000000031</v>
+      </c>
+      <c r="W12" s="117">
+        <f t="shared" ref="W12" si="11">U12-V12</f>
+        <v>346.9458799999997</v>
+      </c>
+      <c r="X12" s="118">
+        <f t="shared" ref="X12:X29" si="12">+IF(IFERROR(U12/V12-1,"-")&lt;300%,IFERROR(U12/V12-1,"-"),"n.a.")</f>
+        <v>0.73202650509664768</v>
+      </c>
+      <c r="Y12" s="117">
+        <f>SUM(Y10:Y11)</f>
+        <v>676.42212142168842</v>
+      </c>
+      <c r="Z12" s="117">
+        <f t="shared" ref="Z12" si="13">U12-Y12</f>
+        <v>144.4763785783116</v>
+      </c>
+      <c r="AA12" s="118">
+        <f t="shared" si="2"/>
+        <v>0.21358907995890863</v>
+      </c>
+      <c r="AC12" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="116">
+        <f>AD10+AD11</f>
+        <v>693.26205000000016</v>
+      </c>
+      <c r="AE12" s="25">
+        <f>SUM(AE10:AE11)</f>
+        <v>132.07731000000007</v>
+      </c>
+      <c r="AF12" s="117">
+        <f t="shared" ref="AF12" si="14">AD12-AE12</f>
+        <v>561.18474000000015</v>
+      </c>
+      <c r="AG12" s="118" t="str">
+        <f t="shared" ref="AG12:AG29" si="15">+IF(IFERROR(AD12/AE12-1,"-")&lt;300%,IFERROR(AD12/AE12-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AH12" s="117">
+        <f>SUM(AH10:AH11)</f>
+        <v>433.29782952995163</v>
+      </c>
+      <c r="AI12" s="117">
+        <f t="shared" ref="AI12" si="16">AD12-AH12</f>
+        <v>259.96422047004853</v>
+      </c>
+      <c r="AJ12" s="118">
+        <f t="shared" si="3"/>
+        <v>0.59996658822884452</v>
+      </c>
+      <c r="AL12" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="116">
+        <f>AM10+AM11</f>
+        <v>9946.4671500000022</v>
+      </c>
+      <c r="AN12" s="25">
+        <f>SUM(AN10:AN11)</f>
+        <v>132.07731000000007</v>
+      </c>
+      <c r="AO12" s="117">
+        <f t="shared" ref="AO12" si="17">AM12-AN12</f>
+        <v>9814.3898400000016</v>
+      </c>
+      <c r="AP12" s="118" t="str">
+        <f t="shared" ref="AP12:AP29" si="18">+IF(IFERROR(AM12/AN12-1,"-")&lt;300%,IFERROR(AM12/AN12-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ12" s="117">
+        <f>SUM(AQ10:AQ11)</f>
+        <v>433.29782952995163</v>
+      </c>
+      <c r="AR12" s="117">
+        <f t="shared" ref="AR12" si="19">AM12-AQ12</f>
+        <v>9513.1693204700514</v>
+      </c>
+      <c r="AS12" s="118" t="str">
+        <f t="shared" si="4"/>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B13" s="87" t="s">
         <v>4</v>
       </c>
@@ -10005,19 +10621,95 @@
       </c>
       <c r="D13" s="119">
         <f>D12/D10</f>
-        <v>0.66455436874798002</v>
+        <v>0.68487598362215729</v>
       </c>
       <c r="E13" s="88"/>
       <c r="F13" s="131"/>
       <c r="G13" s="119">
         <f>G12/G10</f>
-        <v>0.65656565680852641</v>
+        <v>0.65656560214972459</v>
       </c>
       <c r="H13" s="89"/>
       <c r="I13" s="131"/>
       <c r="J13" s="90"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K13" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="119">
+        <f>L12/L10</f>
+        <v>0.66876848798846023</v>
+      </c>
+      <c r="M13" s="119">
+        <f>M12/M10</f>
+        <v>0.48387328202232482</v>
+      </c>
+      <c r="N13" s="88"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="119">
+        <f>P12/P10</f>
+        <v>0.6565656021497247</v>
+      </c>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="131"/>
+      <c r="T13" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13" s="119">
+        <f>U12/U10</f>
+        <v>0.66994524491354424</v>
+      </c>
+      <c r="V13" s="119">
+        <f>V12/V10</f>
+        <v>0.63219041088428052</v>
+      </c>
+      <c r="W13" s="88"/>
+      <c r="X13" s="131"/>
+      <c r="Y13" s="119">
+        <f>Y12/Y10</f>
+        <v>0.65656560214972459</v>
+      </c>
+      <c r="Z13" s="89"/>
+      <c r="AA13" s="131"/>
+      <c r="AC13" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="119">
+        <f>AD12/AD10</f>
+        <v>0.60684311230552457</v>
+      </c>
+      <c r="AE13" s="119">
+        <f>AE12/AE10</f>
+        <v>0.53148537534363882</v>
+      </c>
+      <c r="AF13" s="88"/>
+      <c r="AG13" s="131"/>
+      <c r="AH13" s="119">
+        <f>AH12/AH10</f>
+        <v>0.65656692227048863</v>
+      </c>
+      <c r="AI13" s="89"/>
+      <c r="AJ13" s="131"/>
+      <c r="AL13" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM13" s="119">
+        <f>AM12/AM10</f>
+        <v>0.65523499011857711</v>
+      </c>
+      <c r="AN13" s="119">
+        <f>AN12/AN10</f>
+        <v>0.53148537534363882</v>
+      </c>
+      <c r="AO13" s="88"/>
+      <c r="AP13" s="131"/>
+      <c r="AQ13" s="119">
+        <f>AQ12/AQ10</f>
+        <v>0.65656692227048863</v>
+      </c>
+      <c r="AR13" s="89"/>
+      <c r="AS13" s="131"/>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B14" s="87"/>
       <c r="C14" s="91"/>
       <c r="D14" s="92"/>
@@ -10027,8 +10719,40 @@
       <c r="H14" s="93"/>
       <c r="I14" s="132"/>
       <c r="J14" s="95"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K14" s="87"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="132"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="132"/>
+      <c r="T14" s="87"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="92"/>
+      <c r="W14" s="93"/>
+      <c r="X14" s="132"/>
+      <c r="Y14" s="94"/>
+      <c r="Z14" s="93"/>
+      <c r="AA14" s="132"/>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="92"/>
+      <c r="AF14" s="93"/>
+      <c r="AG14" s="132"/>
+      <c r="AH14" s="94"/>
+      <c r="AI14" s="93"/>
+      <c r="AJ14" s="132"/>
+      <c r="AL14" s="87"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="92"/>
+      <c r="AO14" s="93"/>
+      <c r="AP14" s="132"/>
+      <c r="AQ14" s="94"/>
+      <c r="AR14" s="93"/>
+      <c r="AS14" s="132"/>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B15" s="96" t="s">
         <v>5</v>
       </c>
@@ -10037,32 +10761,156 @@
         <v>-152.63279</v>
       </c>
       <c r="D15" s="3">
-        <f>VLOOKUP(B15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>-1862.5911599999997</v>
+        <f>VLOOKUP(B15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>-133.72119999999998</v>
       </c>
       <c r="E15" s="122">
-        <f t="shared" ref="E15" si="4">C15-D15</f>
-        <v>1709.9583699999998</v>
+        <f t="shared" ref="E15" si="20">C15-D15</f>
+        <v>-18.911590000000018</v>
       </c>
       <c r="F15" s="123">
-        <f t="shared" si="2"/>
-        <v>-0.91805351959256587</v>
+        <f t="shared" si="6"/>
+        <v>0.14142551816765048</v>
       </c>
       <c r="G15" s="124">
-        <f>VLOOKUP(B15,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
-        <v>-2314.5730600000006</v>
+        <f>VLOOKUP(B15,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
+        <v>-174.23000000000002</v>
       </c>
       <c r="H15" s="122">
-        <f t="shared" ref="H15" si="5">C15-G15</f>
-        <v>2161.9402700000005</v>
+        <f t="shared" ref="H15" si="21">C15-G15</f>
+        <v>21.597210000000018</v>
       </c>
       <c r="I15" s="123">
         <f t="shared" si="0"/>
-        <v>-0.93405574762889532</v>
+        <v>-0.12395804396487409</v>
       </c>
       <c r="J15" s="108"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K15" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3">
+        <f>GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","6.- Gastos de personal")/1000</f>
+        <v>-152.63279</v>
+      </c>
+      <c r="M15" s="3">
+        <f>VLOOKUP(K15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>-300.72410999999994</v>
+      </c>
+      <c r="N15" s="122">
+        <f t="shared" ref="N15" si="22">L15-M15</f>
+        <v>148.09131999999994</v>
+      </c>
+      <c r="O15" s="123">
+        <f t="shared" ref="O15:O30" si="23">+IF(IFERROR(L15/M15-1,"-")&lt;300%,IFERROR(L15/M15-1,"-"),"n.a.")</f>
+        <v>-0.49244910891913507</v>
+      </c>
+      <c r="P15" s="124">
+        <f>VLOOKUP(K15,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>-174.23000000000002</v>
+      </c>
+      <c r="Q15" s="122">
+        <f t="shared" ref="Q15" si="24">L15-P15</f>
+        <v>21.597210000000018</v>
+      </c>
+      <c r="R15" s="123">
+        <f t="shared" ref="R15:R30" si="25">+IF(IFERROR(L15/P15-1,"-")&lt;300%,IFERROR(L15/P15-1,"-"),"n.a.")</f>
+        <v>-0.12395804396487409</v>
+      </c>
+      <c r="T15" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
+        <f>GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","6.- Gastos de personal")/1000</f>
+        <v>-152.63279</v>
+      </c>
+      <c r="V15" s="3">
+        <f>VLOOKUP(T15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>-153.08434999999992</v>
+      </c>
+      <c r="W15" s="122">
+        <f t="shared" ref="W15" si="26">U15-V15</f>
+        <v>0.45155999999991536</v>
+      </c>
+      <c r="X15" s="123">
+        <f t="shared" ref="X15:X30" si="27">+IF(IFERROR(U15/V15-1,"-")&lt;300%,IFERROR(U15/V15-1,"-"),"n.a.")</f>
+        <v>-2.9497463326585427E-3</v>
+      </c>
+      <c r="Y15" s="124">
+        <f>VLOOKUP(T15,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>-174.23000000000002</v>
+      </c>
+      <c r="Z15" s="122">
+        <f t="shared" ref="Z15" si="28">U15-Y15</f>
+        <v>21.597210000000018</v>
+      </c>
+      <c r="AA15" s="123">
+        <f t="shared" ref="AA15:AA30" si="29">+IF(IFERROR(U15/Y15-1,"-")&lt;300%,IFERROR(U15/Y15-1,"-"),"n.a.")</f>
+        <v>-0.12395804396487409</v>
+      </c>
+      <c r="AC15" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
+        <f>GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","6.- Gastos de personal")/1000</f>
+        <v>-431.63279</v>
+      </c>
+      <c r="AE15" s="3">
+        <f>VLOOKUP(AC15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-172.01862</v>
+      </c>
+      <c r="AF15" s="122">
+        <f t="shared" ref="AF15" si="30">AD15-AE15</f>
+        <v>-259.61417</v>
+      </c>
+      <c r="AG15" s="123">
+        <f t="shared" ref="AG15:AG30" si="31">+IF(IFERROR(AD15/AE15-1,"-")&lt;300%,IFERROR(AD15/AE15-1,"-"),"n.a.")</f>
+        <v>1.5092213273191009</v>
+      </c>
+      <c r="AH15" s="124">
+        <f>VLOOKUP(AC15,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-306.97666666666669</v>
+      </c>
+      <c r="AI15" s="122">
+        <f t="shared" ref="AI15" si="32">AD15-AH15</f>
+        <v>-124.65612333333331</v>
+      </c>
+      <c r="AJ15" s="123">
+        <f t="shared" ref="AJ15:AJ30" si="33">+IF(IFERROR(AD15/AH15-1,"-")&lt;300%,IFERROR(AD15/AH15-1,"-"),"n.a.")</f>
+        <v>0.4060768679487039</v>
+      </c>
+      <c r="AL15" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
+        <f>GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","6.- Gastos de personal")/1000</f>
+        <v>-2006.5025899999998</v>
+      </c>
+      <c r="AN15" s="3">
+        <f>VLOOKUP(AL15,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-172.01862</v>
+      </c>
+      <c r="AO15" s="122">
+        <f t="shared" ref="AO15" si="34">AM15-AN15</f>
+        <v>-1834.4839699999998</v>
+      </c>
+      <c r="AP15" s="123" t="str">
+        <f t="shared" ref="AP15:AP30" si="35">+IF(IFERROR(AM15/AN15-1,"-")&lt;300%,IFERROR(AM15/AN15-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ15" s="124">
+        <f>VLOOKUP(AL15,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-306.97666666666669</v>
+      </c>
+      <c r="AR15" s="122">
+        <f t="shared" ref="AR15" si="36">AM15-AQ15</f>
+        <v>-1699.5259233333331</v>
+      </c>
+      <c r="AS15" s="123" t="str">
+        <f t="shared" ref="AS15:AS30" si="37">+IF(IFERROR(AM15/AQ15-1,"-")&lt;300%,IFERROR(AM15/AQ15-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="B16" s="97" t="s">
         <v>6</v>
       </c>
@@ -10072,19 +10920,95 @@
       </c>
       <c r="D16" s="102">
         <f>D15/D10</f>
-        <v>-0.14576490786817023</v>
+        <v>-0.15879194000150498</v>
       </c>
       <c r="E16" s="98"/>
       <c r="F16" s="115"/>
       <c r="G16" s="102">
         <f>G15/G10</f>
-        <v>-0.14521444634022745</v>
+        <v>-0.16972077545428679</v>
       </c>
       <c r="H16" s="98"/>
       <c r="I16" s="115"/>
       <c r="J16" s="85"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K16" s="97" t="s">
+        <v>6</v>
+      </c>
+      <c r="L16" s="102">
+        <f>L15/L10</f>
+        <v>-0.16735042111111259</v>
+      </c>
+      <c r="M16" s="102">
+        <f>M15/M10</f>
+        <v>-0.42986166982652202</v>
+      </c>
+      <c r="N16" s="98"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="102">
+        <f>P15/P10</f>
+        <v>-0.21817826162543111</v>
+      </c>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="115"/>
+      <c r="T16" s="97" t="s">
+        <v>6</v>
+      </c>
+      <c r="U16" s="102">
+        <f>U15/U10</f>
+        <v>-0.12456547536435694</v>
+      </c>
+      <c r="V16" s="102">
+        <f>V15/V10</f>
+        <v>-0.20419437311360972</v>
+      </c>
+      <c r="W16" s="98"/>
+      <c r="X16" s="115"/>
+      <c r="Y16" s="102">
+        <f>Y15/Y10</f>
+        <v>-0.16911544025514286</v>
+      </c>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="115"/>
+      <c r="AC16" s="97" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD16" s="102">
+        <f>AD15/AD10</f>
+        <v>-0.3778273823826313</v>
+      </c>
+      <c r="AE16" s="102">
+        <f>AE15/AE10</f>
+        <v>-0.69221110588029644</v>
+      </c>
+      <c r="AF16" s="98"/>
+      <c r="AG16" s="115"/>
+      <c r="AH16" s="102">
+        <f>AH15/AH10</f>
+        <v>-0.46515516927659778</v>
+      </c>
+      <c r="AI16" s="98"/>
+      <c r="AJ16" s="115"/>
+      <c r="AL16" s="97" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM16" s="102">
+        <f>AM15/AM10</f>
+        <v>-0.13218067127799735</v>
+      </c>
+      <c r="AN16" s="102">
+        <f>AN15/AN10</f>
+        <v>-0.69221110588029644</v>
+      </c>
+      <c r="AO16" s="98"/>
+      <c r="AP16" s="115"/>
+      <c r="AQ16" s="102">
+        <f>AQ15/AQ10</f>
+        <v>-0.46515516927659778</v>
+      </c>
+      <c r="AR16" s="98"/>
+      <c r="AS16" s="115"/>
+    </row>
+    <row r="17" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B17" s="97"/>
       <c r="C17" s="99"/>
       <c r="D17" s="99"/>
@@ -10094,8 +11018,40 @@
       <c r="H17" s="84"/>
       <c r="I17" s="115"/>
       <c r="J17" s="85"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K17" s="97"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="115"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="115"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="84"/>
+      <c r="X17" s="115"/>
+      <c r="Y17" s="84"/>
+      <c r="Z17" s="84"/>
+      <c r="AA17" s="115"/>
+      <c r="AC17" s="97"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="115"/>
+      <c r="AH17" s="84"/>
+      <c r="AI17" s="84"/>
+      <c r="AJ17" s="115"/>
+      <c r="AL17" s="97"/>
+      <c r="AM17" s="99"/>
+      <c r="AN17" s="99"/>
+      <c r="AO17" s="84"/>
+      <c r="AP17" s="115"/>
+      <c r="AQ17" s="84"/>
+      <c r="AR17" s="84"/>
+      <c r="AS17" s="115"/>
+    </row>
+    <row r="18" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B18" s="75" t="s">
         <v>7</v>
       </c>
@@ -10104,23 +11060,23 @@
         <v>5.2862</v>
       </c>
       <c r="D18" s="3">
-        <f>VLOOKUP(B18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>49.798200000000001</v>
+        <f>VLOOKUP(B18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>0</v>
       </c>
       <c r="E18" s="122">
-        <f t="shared" ref="E18:E20" si="6">C18-D18</f>
-        <v>-44.512</v>
-      </c>
-      <c r="F18" s="115">
-        <f t="shared" si="2"/>
-        <v>-0.89384756878762683</v>
+        <f t="shared" ref="E18:E20" si="38">C18-D18</f>
+        <v>5.2862</v>
+      </c>
+      <c r="F18" s="115" t="str">
+        <f t="shared" si="6"/>
+        <v>n.a.</v>
       </c>
       <c r="G18" s="121">
-        <f>VLOOKUP(B18,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
+        <f>VLOOKUP(B18,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
         <v>0</v>
       </c>
       <c r="H18" s="114">
-        <f t="shared" ref="H18:H20" si="7">C18-G18</f>
+        <f t="shared" ref="H18:H20" si="39">C18-G18</f>
         <v>5.2862</v>
       </c>
       <c r="I18" s="115" t="str">
@@ -10128,8 +11084,132 @@
         <v>n.a.</v>
       </c>
       <c r="J18" s="85"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K18" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="23">
+        <f>GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","5.- Otros ingresos de explotación")/1000</f>
+        <v>10.013669999999999</v>
+      </c>
+      <c r="M18" s="3">
+        <f>VLOOKUP(K18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>1.8009600000000001</v>
+      </c>
+      <c r="N18" s="122">
+        <f t="shared" ref="N18:N20" si="40">L18-M18</f>
+        <v>8.2127099999999995</v>
+      </c>
+      <c r="O18" s="115" t="str">
+        <f t="shared" ref="O18:O30" si="41">+IF(IFERROR(L18/M18-1,"-")&lt;300%,IFERROR(L18/M18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="P18" s="121">
+        <f>VLOOKUP(K18,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="114">
+        <f t="shared" ref="Q18:Q20" si="42">L18-P18</f>
+        <v>10.013669999999999</v>
+      </c>
+      <c r="R18" s="115" t="str">
+        <f t="shared" ref="R18:R30" si="43">+IF(IFERROR(L18/P18-1,"-")&lt;300%,IFERROR(L18/P18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="T18" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="U18" s="23">
+        <f>GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","5.- Otros ingresos de explotación")/1000</f>
+        <v>13.461829999999999</v>
+      </c>
+      <c r="V18" s="3">
+        <f>VLOOKUP(T18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="122">
+        <f t="shared" ref="W18:W20" si="44">U18-V18</f>
+        <v>13.461829999999999</v>
+      </c>
+      <c r="X18" s="115" t="str">
+        <f t="shared" ref="X18:X30" si="45">+IF(IFERROR(U18/V18-1,"-")&lt;300%,IFERROR(U18/V18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="Y18" s="121">
+        <f>VLOOKUP(T18,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="114">
+        <f t="shared" ref="Z18:Z20" si="46">U18-Y18</f>
+        <v>13.461829999999999</v>
+      </c>
+      <c r="AA18" s="115" t="str">
+        <f t="shared" ref="AA18:AA30" si="47">+IF(IFERROR(U18/Y18-1,"-")&lt;300%,IFERROR(U18/Y18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AC18" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD18" s="23">
+        <f>GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","5.- Otros ingresos de explotación")/1000</f>
+        <v>14.533940000000001</v>
+      </c>
+      <c r="AE18" s="3">
+        <f>VLOOKUP(AC18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>47.204360000000001</v>
+      </c>
+      <c r="AF18" s="122">
+        <f t="shared" ref="AF18:AF20" si="48">AD18-AE18</f>
+        <v>-32.67042</v>
+      </c>
+      <c r="AG18" s="115">
+        <f t="shared" ref="AG18:AG30" si="49">+IF(IFERROR(AD18/AE18-1,"-")&lt;300%,IFERROR(AD18/AE18-1,"-"),"n.a.")</f>
+        <v>-0.69210598343034413</v>
+      </c>
+      <c r="AH18" s="121">
+        <f>VLOOKUP(AC18,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="114">
+        <f t="shared" ref="AI18:AI20" si="50">AD18-AH18</f>
+        <v>14.533940000000001</v>
+      </c>
+      <c r="AJ18" s="115" t="str">
+        <f t="shared" ref="AJ18:AJ30" si="51">+IF(IFERROR(AD18/AH18-1,"-")&lt;300%,IFERROR(AD18/AH18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AL18" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM18" s="23">
+        <f>GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","5.- Otros ingresos de explotación")/1000</f>
+        <v>114.62098</v>
+      </c>
+      <c r="AN18" s="3">
+        <f>VLOOKUP(AL18,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>47.204360000000001</v>
+      </c>
+      <c r="AO18" s="122">
+        <f t="shared" ref="AO18:AO20" si="52">AM18-AN18</f>
+        <v>67.416619999999995</v>
+      </c>
+      <c r="AP18" s="115">
+        <f t="shared" ref="AP18:AP30" si="53">+IF(IFERROR(AM18/AN18-1,"-")&lt;300%,IFERROR(AM18/AN18-1,"-"),"n.a.")</f>
+        <v>1.4281862946558328</v>
+      </c>
+      <c r="AQ18" s="121">
+        <f>VLOOKUP(AL18,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="114">
+        <f t="shared" ref="AR18:AR20" si="54">AM18-AQ18</f>
+        <v>114.62098</v>
+      </c>
+      <c r="AS18" s="115" t="str">
+        <f t="shared" ref="AS18:AS30" si="55">+IF(IFERROR(AM18/AQ18-1,"-")&lt;300%,IFERROR(AM18/AQ18-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="19" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B19" s="75" t="s">
         <v>8</v>
       </c>
@@ -10138,32 +11218,156 @@
         <v>-100</v>
       </c>
       <c r="D19" s="3">
-        <f>VLOOKUP(B19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>-1253.9292399999999</v>
+        <f>VLOOKUP(B19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>-73.912790000000001</v>
       </c>
       <c r="E19" s="113">
+        <f t="shared" si="38"/>
+        <v>-26.087209999999999</v>
+      </c>
+      <c r="F19" s="115">
         <f t="shared" si="6"/>
-        <v>1153.9292399999999</v>
-      </c>
-      <c r="F19" s="115">
-        <f t="shared" si="2"/>
-        <v>-0.92025068336391935</v>
+        <v>0.35294581627888766</v>
       </c>
       <c r="G19" s="121">
-        <f>VLOOKUP(B19,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
-        <v>-1729.9999999599997</v>
+        <f>VLOOKUP(B19,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
+        <v>-120.05332916333333</v>
       </c>
       <c r="H19" s="113">
-        <f t="shared" si="7"/>
-        <v>1629.9999999599997</v>
+        <f t="shared" si="39"/>
+        <v>20.053329163333331</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="0"/>
-        <v>-0.94219653179057106</v>
+        <v>-0.1670368435684999</v>
       </c>
       <c r="J19" s="109"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K19" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="3">
+        <f>GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","7.- Otros gastos de explotación")/1000</f>
+        <v>-141.64847</v>
+      </c>
+      <c r="M19" s="3">
+        <f>VLOOKUP(K19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>-122.16905</v>
+      </c>
+      <c r="N19" s="113">
+        <f t="shared" si="40"/>
+        <v>-19.479420000000005</v>
+      </c>
+      <c r="O19" s="115">
+        <f t="shared" si="41"/>
+        <v>0.15944643917587964</v>
+      </c>
+      <c r="P19" s="121">
+        <f>VLOOKUP(K19,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>-144.84268916333332</v>
+      </c>
+      <c r="Q19" s="113">
+        <f t="shared" si="42"/>
+        <v>3.1942191633333152</v>
+      </c>
+      <c r="R19" s="115">
+        <f t="shared" si="43"/>
+        <v>-2.2053023054075749E-2</v>
+      </c>
+      <c r="T19" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="U19" s="3">
+        <f>GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","7.- Otros gastos de explotación")/1000</f>
+        <v>-149.83611999999999</v>
+      </c>
+      <c r="V19" s="3">
+        <f>VLOOKUP(T19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>-68.327619999999996</v>
+      </c>
+      <c r="W19" s="113">
+        <f t="shared" si="44"/>
+        <v>-81.508499999999998</v>
+      </c>
+      <c r="X19" s="115">
+        <f t="shared" si="45"/>
+        <v>1.1929070557411485</v>
+      </c>
+      <c r="Y19" s="121">
+        <f>VLOOKUP(T19,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>-148.9926891633333</v>
+      </c>
+      <c r="Z19" s="113">
+        <f t="shared" si="46"/>
+        <v>-0.84343083666669827</v>
+      </c>
+      <c r="AA19" s="115">
+        <f t="shared" si="47"/>
+        <v>5.6608873992607389E-3</v>
+      </c>
+      <c r="AC19" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD19" s="3">
+        <f>GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","7.- Otros gastos de explotación")/1000</f>
+        <v>-291.51097000000027</v>
+      </c>
+      <c r="AE19" s="3">
+        <f>VLOOKUP(AC19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-239.07332000000005</v>
+      </c>
+      <c r="AF19" s="113">
+        <f t="shared" si="48"/>
+        <v>-52.437650000000218</v>
+      </c>
+      <c r="AG19" s="115">
+        <f t="shared" si="49"/>
+        <v>0.21933710545367502</v>
+      </c>
+      <c r="AH19" s="121">
+        <f>VLOOKUP(AC19,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-180.34268916333332</v>
+      </c>
+      <c r="AI19" s="113">
+        <f t="shared" si="50"/>
+        <v>-111.16828083666695</v>
+      </c>
+      <c r="AJ19" s="115">
+        <f t="shared" si="51"/>
+        <v>0.61642798691985634</v>
+      </c>
+      <c r="AL19" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM19" s="3">
+        <f>GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","7.- Otros gastos de explotación")/1000</f>
+        <v>-1678.4074352502942</v>
+      </c>
+      <c r="AN19" s="3">
+        <f>VLOOKUP(AL19,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-239.07332000000005</v>
+      </c>
+      <c r="AO19" s="113">
+        <f t="shared" si="52"/>
+        <v>-1439.3341152502942</v>
+      </c>
+      <c r="AP19" s="115" t="str">
+        <f t="shared" si="53"/>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ19" s="121">
+        <f>VLOOKUP(AL19,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-180.34268916333332</v>
+      </c>
+      <c r="AR19" s="113">
+        <f t="shared" si="54"/>
+        <v>-1498.0647460869609</v>
+      </c>
+      <c r="AS19" s="115" t="str">
+        <f t="shared" si="55"/>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="20" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B20" s="100" t="s">
         <v>9</v>
       </c>
@@ -10173,31 +11377,155 @@
       </c>
       <c r="D20" s="7">
         <f>SUM(D18:D19)</f>
-        <v>-1204.13104</v>
+        <v>-73.912790000000001</v>
       </c>
       <c r="E20" s="7">
+        <f t="shared" si="38"/>
+        <v>-20.801010000000005</v>
+      </c>
+      <c r="F20" s="125">
         <f t="shared" si="6"/>
-        <v>1109.41724</v>
-      </c>
-      <c r="F20" s="125">
-        <f t="shared" si="2"/>
-        <v>-0.92134261400652873</v>
+        <v>0.28142639453875318</v>
       </c>
       <c r="G20" s="7">
         <f>SUM(G18:G19)</f>
-        <v>-1729.9999999599997</v>
+        <v>-120.05332916333333</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="7"/>
-        <v>1635.2861999599997</v>
+        <f t="shared" si="39"/>
+        <v>25.339529163333324</v>
       </c>
       <c r="I20" s="125">
         <f t="shared" si="0"/>
-        <v>-0.94525213872705782</v>
+        <v>-0.21106894194378178</v>
       </c>
       <c r="J20" s="107"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K20" s="100" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="7">
+        <f>SUM(L18:L19)</f>
+        <v>-131.63480000000001</v>
+      </c>
+      <c r="M20" s="7">
+        <f>SUM(M18:M19)</f>
+        <v>-120.36809</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="40"/>
+        <v>-11.266710000000018</v>
+      </c>
+      <c r="O20" s="125">
+        <f t="shared" si="41"/>
+        <v>9.3602133256413866E-2</v>
+      </c>
+      <c r="P20" s="7">
+        <f>SUM(P18:P19)</f>
+        <v>-144.84268916333332</v>
+      </c>
+      <c r="Q20" s="7">
+        <f t="shared" si="42"/>
+        <v>13.207889163333306</v>
+      </c>
+      <c r="R20" s="125">
+        <f t="shared" si="43"/>
+        <v>-9.1187820659966445E-2</v>
+      </c>
+      <c r="T20" s="100" t="s">
+        <v>9</v>
+      </c>
+      <c r="U20" s="7">
+        <f>SUM(U18:U19)</f>
+        <v>-136.37429</v>
+      </c>
+      <c r="V20" s="7">
+        <f>SUM(V18:V19)</f>
+        <v>-68.327619999999996</v>
+      </c>
+      <c r="W20" s="7">
+        <f t="shared" si="44"/>
+        <v>-68.046670000000006</v>
+      </c>
+      <c r="X20" s="125">
+        <f t="shared" si="45"/>
+        <v>0.99588819279816865</v>
+      </c>
+      <c r="Y20" s="7">
+        <f>SUM(Y18:Y19)</f>
+        <v>-148.9926891633333</v>
+      </c>
+      <c r="Z20" s="7">
+        <f t="shared" si="46"/>
+        <v>12.618399163333294</v>
+      </c>
+      <c r="AA20" s="125">
+        <f t="shared" si="47"/>
+        <v>-8.4691398176593546E-2</v>
+      </c>
+      <c r="AC20" s="100" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="7">
+        <f>SUM(AD18:AD19)</f>
+        <v>-276.97703000000024</v>
+      </c>
+      <c r="AE20" s="7">
+        <f>SUM(AE18:AE19)</f>
+        <v>-191.86896000000004</v>
+      </c>
+      <c r="AF20" s="7">
+        <f t="shared" si="48"/>
+        <v>-85.108070000000197</v>
+      </c>
+      <c r="AG20" s="125">
+        <f t="shared" si="49"/>
+        <v>0.44357393712875792</v>
+      </c>
+      <c r="AH20" s="7">
+        <f>SUM(AH18:AH19)</f>
+        <v>-180.34268916333332</v>
+      </c>
+      <c r="AI20" s="7">
+        <f t="shared" si="50"/>
+        <v>-96.634340836666922</v>
+      </c>
+      <c r="AJ20" s="125">
+        <f t="shared" si="51"/>
+        <v>0.535837306657587</v>
+      </c>
+      <c r="AL20" s="100" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM20" s="7">
+        <f>SUM(AM18:AM19)</f>
+        <v>-1563.7864552502942</v>
+      </c>
+      <c r="AN20" s="7">
+        <f>SUM(AN18:AN19)</f>
+        <v>-191.86896000000004</v>
+      </c>
+      <c r="AO20" s="7">
+        <f t="shared" si="52"/>
+        <v>-1371.9174952502942</v>
+      </c>
+      <c r="AP20" s="125" t="str">
+        <f t="shared" si="53"/>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ20" s="7">
+        <f>SUM(AQ18:AQ19)</f>
+        <v>-180.34268916333332</v>
+      </c>
+      <c r="AR20" s="7">
+        <f t="shared" si="54"/>
+        <v>-1383.443766086961</v>
+      </c>
+      <c r="AS20" s="125" t="str">
+        <f t="shared" si="55"/>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="21" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B21" s="75" t="s">
         <v>6</v>
       </c>
@@ -10207,19 +11535,95 @@
       </c>
       <c r="D21" s="102">
         <f>D20/D10</f>
-        <v>-9.4234340780831385E-2</v>
+        <v>-8.7770340940881778E-2</v>
       </c>
       <c r="E21" s="84"/>
       <c r="F21" s="115"/>
       <c r="G21" s="102">
         <f>G20/G10</f>
-        <v>-0.10853880419863902</v>
+        <v>-0.11694624416845362</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="115"/>
       <c r="J21" s="85"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K21" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="102">
+        <f>L20/L10</f>
+        <v>-0.14432769795321887</v>
+      </c>
+      <c r="M21" s="102">
+        <f>M20/M10</f>
+        <v>-0.17205680037170645</v>
+      </c>
+      <c r="N21" s="84"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="102">
+        <f>P20/P10</f>
+        <v>-0.18137821345812277</v>
+      </c>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="115"/>
+      <c r="T21" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="U21" s="102">
+        <f>U20/U10</f>
+        <v>-0.11129671587164638</v>
+      </c>
+      <c r="V21" s="102">
+        <f>V20/V10</f>
+        <v>-9.1140051430763161E-2</v>
+      </c>
+      <c r="W21" s="84"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="102">
+        <f>Y20/Y10</f>
+        <v>-0.14461897619614739</v>
+      </c>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="115"/>
+      <c r="AC21" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD21" s="102">
+        <f>AD20/AD10</f>
+        <v>-0.24245031575338757</v>
+      </c>
+      <c r="AE21" s="102">
+        <f>AE20/AE10</f>
+        <v>-0.77208981786798658</v>
+      </c>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="115"/>
+      <c r="AH21" s="102">
+        <f>AH20/AH10</f>
+        <v>-0.27326941495738166</v>
+      </c>
+      <c r="AI21" s="84"/>
+      <c r="AJ21" s="115"/>
+      <c r="AL21" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM21" s="102">
+        <f>AM20/AM10</f>
+        <v>-0.10301623552373479</v>
+      </c>
+      <c r="AN21" s="102">
+        <f>AN20/AN10</f>
+        <v>-0.77208981786798658</v>
+      </c>
+      <c r="AO21" s="84"/>
+      <c r="AP21" s="115"/>
+      <c r="AQ21" s="102">
+        <f>AQ20/AQ10</f>
+        <v>-0.27326941495738166</v>
+      </c>
+      <c r="AR21" s="84"/>
+      <c r="AS21" s="115"/>
+    </row>
+    <row r="22" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B22" s="101" t="s">
         <v>10</v>
       </c>
@@ -10229,31 +11633,155 @@
       </c>
       <c r="D22" s="24">
         <f>D20+D15</f>
-        <v>-3066.7221999999997</v>
+        <v>-207.63398999999998</v>
       </c>
       <c r="E22" s="126">
-        <f t="shared" ref="E22" si="8">C22-D22</f>
-        <v>2819.3756099999996</v>
+        <f t="shared" ref="E22" si="56">C22-D22</f>
+        <v>-39.712600000000009</v>
       </c>
       <c r="F22" s="133">
         <f>+IF(IFERROR(C22/D22-1,"-")&lt;300%,IFERROR(C22/D22-1,"-"),"n.a.")</f>
-        <v>-0.91934496381837261</v>
+        <v>0.19126251920506854</v>
       </c>
       <c r="G22" s="24">
         <f>G20+G15</f>
-        <v>-4044.5730599600001</v>
+        <v>-294.28332916333335</v>
       </c>
       <c r="H22" s="24">
-        <f t="shared" ref="H22" si="9">C22-G22</f>
-        <v>3797.22646996</v>
+        <f t="shared" ref="H22" si="57">C22-G22</f>
+        <v>46.936739163333357</v>
       </c>
       <c r="I22" s="133">
         <f t="shared" si="0"/>
-        <v>-0.93884482086659449</v>
+        <v>-0.15949506652917633</v>
       </c>
       <c r="J22" s="110"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K22" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="24">
+        <f>L20+L15</f>
+        <v>-284.26759000000004</v>
+      </c>
+      <c r="M22" s="24">
+        <f>M20+M15</f>
+        <v>-421.09219999999993</v>
+      </c>
+      <c r="N22" s="126">
+        <f t="shared" ref="N22" si="58">L22-M22</f>
+        <v>136.82460999999989</v>
+      </c>
+      <c r="O22" s="133">
+        <f>+IF(IFERROR(L22/M22-1,"-")&lt;300%,IFERROR(L22/M22-1,"-"),"n.a.")</f>
+        <v>-0.32492791364931461</v>
+      </c>
+      <c r="P22" s="24">
+        <f>P20+P15</f>
+        <v>-319.07268916333334</v>
+      </c>
+      <c r="Q22" s="24">
+        <f t="shared" ref="Q22" si="59">L22-P22</f>
+        <v>34.805099163333296</v>
+      </c>
+      <c r="R22" s="133">
+        <f t="shared" ref="R22:R30" si="60">+IF(IFERROR(L22/P22-1,"-")&lt;300%,IFERROR(L22/P22-1,"-"),"n.a.")</f>
+        <v>-0.10908203787230619</v>
+      </c>
+      <c r="T22" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="U22" s="24">
+        <f>U20+U15</f>
+        <v>-289.00707999999997</v>
+      </c>
+      <c r="V22" s="24">
+        <f>V20+V15</f>
+        <v>-221.41196999999991</v>
+      </c>
+      <c r="W22" s="126">
+        <f t="shared" ref="W22" si="61">U22-V22</f>
+        <v>-67.595110000000062</v>
+      </c>
+      <c r="X22" s="133">
+        <f>+IF(IFERROR(U22/V22-1,"-")&lt;300%,IFERROR(U22/V22-1,"-"),"n.a.")</f>
+        <v>0.30529112766577193</v>
+      </c>
+      <c r="Y22" s="24">
+        <f>Y20+Y15</f>
+        <v>-323.22268916333331</v>
+      </c>
+      <c r="Z22" s="24">
+        <f t="shared" ref="Z22" si="62">U22-Y22</f>
+        <v>34.21560916333334</v>
+      </c>
+      <c r="AA22" s="133">
+        <f t="shared" ref="AA22:AA30" si="63">+IF(IFERROR(U22/Y22-1,"-")&lt;300%,IFERROR(U22/Y22-1,"-"),"n.a.")</f>
+        <v>-0.1058576959801335</v>
+      </c>
+      <c r="AC22" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="24">
+        <f>AD20+AD15</f>
+        <v>-708.60982000000024</v>
+      </c>
+      <c r="AE22" s="24">
+        <f>AE20+AE15</f>
+        <v>-363.88758000000007</v>
+      </c>
+      <c r="AF22" s="126">
+        <f t="shared" ref="AF22" si="64">AD22-AE22</f>
+        <v>-344.72224000000017</v>
+      </c>
+      <c r="AG22" s="133">
+        <f>+IF(IFERROR(AD22/AE22-1,"-")&lt;300%,IFERROR(AD22/AE22-1,"-"),"n.a.")</f>
+        <v>0.94733170063127758</v>
+      </c>
+      <c r="AH22" s="24">
+        <f>AH20+AH15</f>
+        <v>-487.31935583000001</v>
+      </c>
+      <c r="AI22" s="24">
+        <f t="shared" ref="AI22" si="65">AD22-AH22</f>
+        <v>-221.29046417000023</v>
+      </c>
+      <c r="AJ22" s="133">
+        <f t="shared" ref="AJ22:AJ30" si="66">+IF(IFERROR(AD22/AH22-1,"-")&lt;300%,IFERROR(AD22/AH22-1,"-"),"n.a.")</f>
+        <v>0.4540974240456741</v>
+      </c>
+      <c r="AL22" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM22" s="24">
+        <f>AM20+AM15</f>
+        <v>-3570.2890452502943</v>
+      </c>
+      <c r="AN22" s="24">
+        <f>AN20+AN15</f>
+        <v>-363.88758000000007</v>
+      </c>
+      <c r="AO22" s="126">
+        <f t="shared" ref="AO22" si="67">AM22-AN22</f>
+        <v>-3206.4014652502942</v>
+      </c>
+      <c r="AP22" s="133" t="str">
+        <f>+IF(IFERROR(AM22/AN22-1,"-")&lt;300%,IFERROR(AM22/AN22-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ22" s="24">
+        <f>AQ20+AQ15</f>
+        <v>-487.31935583000001</v>
+      </c>
+      <c r="AR22" s="24">
+        <f t="shared" ref="AR22" si="68">AM22-AQ22</f>
+        <v>-3082.9696894202943</v>
+      </c>
+      <c r="AS22" s="133" t="str">
+        <f t="shared" ref="AS22:AS30" si="69">+IF(IFERROR(AM22/AQ22-1,"-")&lt;300%,IFERROR(AM22/AQ22-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="23" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B23" s="75" t="s">
         <v>6</v>
       </c>
@@ -10263,19 +11791,95 @@
       </c>
       <c r="D23" s="102">
         <f>D22/D10</f>
-        <v>-0.23999924864900163</v>
+        <v>-0.24656228094238675</v>
       </c>
       <c r="E23" s="84"/>
       <c r="F23" s="115"/>
       <c r="G23" s="102">
         <f>G22/G10</f>
-        <v>-0.25375325053886644</v>
+        <v>-0.28666701962274044</v>
       </c>
       <c r="H23" s="84"/>
       <c r="I23" s="115"/>
       <c r="J23" s="85"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K23" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="102">
+        <f>L22/L10</f>
+        <v>-0.31167811906433146</v>
+      </c>
+      <c r="M23" s="102">
+        <f>M22/M10</f>
+        <v>-0.60191847019822842</v>
+      </c>
+      <c r="N23" s="84"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="102">
+        <f>P22/P10</f>
+        <v>-0.39955647508355391</v>
+      </c>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="115"/>
+      <c r="T23" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="U23" s="102">
+        <f>U22/U10</f>
+        <v>-0.2358621912360033</v>
+      </c>
+      <c r="V23" s="102">
+        <f>V22/V10</f>
+        <v>-0.29533442454437292</v>
+      </c>
+      <c r="W23" s="84"/>
+      <c r="X23" s="115"/>
+      <c r="Y23" s="102">
+        <f>Y22/Y10</f>
+        <v>-0.31373441645129024</v>
+      </c>
+      <c r="Z23" s="84"/>
+      <c r="AA23" s="115"/>
+      <c r="AC23" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD23" s="102">
+        <f>AD22/AD10</f>
+        <v>-0.62027769813601885</v>
+      </c>
+      <c r="AE23" s="102">
+        <f>AE22/AE10</f>
+        <v>-1.4643009237482831</v>
+      </c>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="115"/>
+      <c r="AH23" s="102">
+        <f>AH22/AH10</f>
+        <v>-0.73842458423397939</v>
+      </c>
+      <c r="AI23" s="84"/>
+      <c r="AJ23" s="115"/>
+      <c r="AL23" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM23" s="102">
+        <f>AM22/AM10</f>
+        <v>-0.23519690680173214</v>
+      </c>
+      <c r="AN23" s="102">
+        <f>AN22/AN10</f>
+        <v>-1.4643009237482831</v>
+      </c>
+      <c r="AO23" s="84"/>
+      <c r="AP23" s="115"/>
+      <c r="AQ23" s="102">
+        <f>AQ22/AQ10</f>
+        <v>-0.73842458423397939</v>
+      </c>
+      <c r="AR23" s="84"/>
+      <c r="AS23" s="115"/>
+    </row>
+    <row r="24" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B24" s="83" t="s">
         <v>11</v>
       </c>
@@ -10285,31 +11889,155 @@
       </c>
       <c r="D24" s="112">
         <f>D12+D22</f>
-        <v>5424.986200000003</v>
+        <v>369.1108900000001</v>
       </c>
       <c r="E24" s="112">
-        <f t="shared" ref="E24" si="10">C24-D24</f>
-        <v>-5269.2490500000031</v>
+        <f t="shared" ref="E24" si="70">C24-D24</f>
+        <v>-213.37374000000011</v>
       </c>
       <c r="F24" s="127">
-        <f t="shared" si="2"/>
-        <v>-0.97129261821901047</v>
+        <f t="shared" si="6"/>
+        <v>-0.57807489776310872</v>
       </c>
       <c r="G24" s="112">
         <f>G12+G22</f>
-        <v>6420.4269429304904</v>
+        <v>379.72622892613975</v>
       </c>
       <c r="H24" s="112">
-        <f t="shared" ref="H24" si="11">C24-G24</f>
-        <v>-6264.6897929304905</v>
+        <f t="shared" ref="H24" si="71">C24-G24</f>
+        <v>-223.98907892613977</v>
       </c>
       <c r="I24" s="127">
         <f t="shared" si="0"/>
-        <v>-0.97574349005380689</v>
+        <v>-0.58986991643842357</v>
       </c>
       <c r="J24" s="108"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K24" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="L24" s="112">
+        <f>L12+L22</f>
+        <v>325.68606</v>
+      </c>
+      <c r="M24" s="112">
+        <f>M12+M22</f>
+        <v>-82.582459999998093</v>
+      </c>
+      <c r="N24" s="112">
+        <f t="shared" ref="N24" si="72">L24-M24</f>
+        <v>408.26851999999809</v>
+      </c>
+      <c r="O24" s="127">
+        <f t="shared" ref="O24:O30" si="73">+IF(IFERROR(L24/M24-1,"-")&lt;300%,IFERROR(L24/M24-1,"-"),"n.a.")</f>
+        <v>-4.9437679623494812</v>
+      </c>
+      <c r="P24" s="112">
+        <f>P12+P22</f>
+        <v>205.2390548679644</v>
+      </c>
+      <c r="Q24" s="112">
+        <f t="shared" ref="Q24" si="74">L24-P24</f>
+        <v>120.4470051320356</v>
+      </c>
+      <c r="R24" s="127">
+        <f t="shared" ref="R24:R30" si="75">+IF(IFERROR(L24/P24-1,"-")&lt;300%,IFERROR(L24/P24-1,"-"),"n.a.")</f>
+        <v>0.58686201419862449</v>
+      </c>
+      <c r="T24" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="U24" s="112">
+        <f>U12+U22</f>
+        <v>531.89142000000004</v>
+      </c>
+      <c r="V24" s="112">
+        <f>V12+V22</f>
+        <v>252.5406500000004</v>
+      </c>
+      <c r="W24" s="112">
+        <f t="shared" ref="W24" si="76">U24-V24</f>
+        <v>279.35076999999967</v>
+      </c>
+      <c r="X24" s="127">
+        <f t="shared" ref="X24:X30" si="77">+IF(IFERROR(U24/V24-1,"-")&lt;300%,IFERROR(U24/V24-1,"-"),"n.a.")</f>
+        <v>1.1061616021024703</v>
+      </c>
+      <c r="Y24" s="112">
+        <f>Y12+Y22</f>
+        <v>353.1994322583551</v>
+      </c>
+      <c r="Z24" s="112">
+        <f t="shared" ref="Z24" si="78">U24-Y24</f>
+        <v>178.69198774164494</v>
+      </c>
+      <c r="AA24" s="127">
+        <f t="shared" ref="AA24:AA30" si="79">+IF(IFERROR(U24/Y24-1,"-")&lt;300%,IFERROR(U24/Y24-1,"-"),"n.a.")</f>
+        <v>0.50592376833419417</v>
+      </c>
+      <c r="AC24" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD24" s="112">
+        <f>AD12+AD22</f>
+        <v>-15.347770000000082</v>
+      </c>
+      <c r="AE24" s="112">
+        <f>AE12+AE22</f>
+        <v>-231.81027</v>
+      </c>
+      <c r="AF24" s="112">
+        <f t="shared" ref="AF24" si="80">AD24-AE24</f>
+        <v>216.46249999999992</v>
+      </c>
+      <c r="AG24" s="127">
+        <f t="shared" ref="AG24:AG30" si="81">+IF(IFERROR(AD24/AE24-1,"-")&lt;300%,IFERROR(AD24/AE24-1,"-"),"n.a.")</f>
+        <v>-0.93379167368210181</v>
+      </c>
+      <c r="AH24" s="112">
+        <f>AH12+AH22</f>
+        <v>-54.021526300048379</v>
+      </c>
+      <c r="AI24" s="112">
+        <f t="shared" ref="AI24" si="82">AD24-AH24</f>
+        <v>38.673756300048296</v>
+      </c>
+      <c r="AJ24" s="127">
+        <f t="shared" ref="AJ24:AJ30" si="83">+IF(IFERROR(AD24/AH24-1,"-")&lt;300%,IFERROR(AD24/AH24-1,"-"),"n.a.")</f>
+        <v>-0.71589529117050632</v>
+      </c>
+      <c r="AL24" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM24" s="112">
+        <f>AM12+AM22</f>
+        <v>6376.1781047497079</v>
+      </c>
+      <c r="AN24" s="112">
+        <f>AN12+AN22</f>
+        <v>-231.81027</v>
+      </c>
+      <c r="AO24" s="112">
+        <f t="shared" ref="AO24" si="84">AM24-AN24</f>
+        <v>6607.9883747497079</v>
+      </c>
+      <c r="AP24" s="127">
+        <f t="shared" ref="AP24:AP30" si="85">+IF(IFERROR(AM24/AN24-1,"-")&lt;300%,IFERROR(AM24/AN24-1,"-"),"n.a.")</f>
+        <v>-28.506020784798309</v>
+      </c>
+      <c r="AQ24" s="112">
+        <f>AQ12+AQ22</f>
+        <v>-54.021526300048379</v>
+      </c>
+      <c r="AR24" s="112">
+        <f t="shared" ref="AR24" si="86">AM24-AQ24</f>
+        <v>6430.1996310497561</v>
+      </c>
+      <c r="AS24" s="127">
+        <f t="shared" ref="AS24:AS30" si="87">+IF(IFERROR(AM24/AQ24-1,"-")&lt;300%,IFERROR(AM24/AQ24-1,"-"),"n.a.")</f>
+        <v>-119.03032127109667</v>
+      </c>
+    </row>
+    <row r="25" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B25" s="87" t="s">
         <v>12</v>
       </c>
@@ -10319,22 +12047,110 @@
       </c>
       <c r="D25" s="102">
         <f>D24/D10</f>
-        <v>0.42455512009897839</v>
+        <v>0.43831370267977054</v>
       </c>
       <c r="E25" s="89"/>
       <c r="F25" s="134">
-        <f t="shared" si="2"/>
-        <v>-0.24066097538400444</v>
+        <f t="shared" si="6"/>
+        <v>-0.26449648089780342</v>
       </c>
       <c r="G25" s="102">
         <f>G24/G10</f>
-        <v>0.40281240626965992</v>
+        <v>0.36989858252698421</v>
       </c>
       <c r="H25" s="89"/>
       <c r="I25" s="134"/>
       <c r="J25" s="90"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K25" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="102">
+        <f>L24/L10</f>
+        <v>0.35709036892412882</v>
+      </c>
+      <c r="M25" s="102">
+        <f>M24/M10</f>
+        <v>-0.11804518817590365</v>
+      </c>
+      <c r="N25" s="89"/>
+      <c r="O25" s="134">
+        <f t="shared" si="73"/>
+        <v>-4.0250311295367229</v>
+      </c>
+      <c r="P25" s="102">
+        <f>P24/P10</f>
+        <v>0.25700912706617085</v>
+      </c>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="134"/>
+      <c r="T25" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="U25" s="102">
+        <f>U24/U10</f>
+        <v>0.43408305367754096</v>
+      </c>
+      <c r="V25" s="102">
+        <f>V24/V10</f>
+        <v>0.3368559863399076</v>
+      </c>
+      <c r="W25" s="89"/>
+      <c r="X25" s="134">
+        <f t="shared" si="77"/>
+        <v>0.28863096183639003</v>
+      </c>
+      <c r="Y25" s="102">
+        <f>Y24/Y10</f>
+        <v>0.3428311856984344</v>
+      </c>
+      <c r="Z25" s="89"/>
+      <c r="AA25" s="134"/>
+      <c r="AC25" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD25" s="102">
+        <f>AD24/AD10</f>
+        <v>-1.3434585830494268E-2</v>
+      </c>
+      <c r="AE25" s="102">
+        <f>AE24/AE10</f>
+        <v>-0.9328155484046442</v>
+      </c>
+      <c r="AF25" s="89"/>
+      <c r="AG25" s="134">
+        <f t="shared" si="81"/>
+        <v>-0.98559781099975141</v>
+      </c>
+      <c r="AH25" s="102">
+        <f>AH24/AH10</f>
+        <v>-8.1857661963490758E-2</v>
+      </c>
+      <c r="AI25" s="89"/>
+      <c r="AJ25" s="134"/>
+      <c r="AL25" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM25" s="102">
+        <f>AM24/AM10</f>
+        <v>0.420038083316845</v>
+      </c>
+      <c r="AN25" s="102">
+        <f>AN24/AN10</f>
+        <v>-0.9328155484046442</v>
+      </c>
+      <c r="AO25" s="89"/>
+      <c r="AP25" s="134">
+        <f t="shared" si="85"/>
+        <v>-1.4502906110808496</v>
+      </c>
+      <c r="AQ25" s="102">
+        <f>AQ24/AQ10</f>
+        <v>-8.1857661963490758E-2</v>
+      </c>
+      <c r="AR25" s="89"/>
+      <c r="AS25" s="134"/>
+    </row>
+    <row r="26" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B26" s="87"/>
       <c r="C26" s="92"/>
       <c r="D26" s="92"/>
@@ -10344,8 +12160,40 @@
       <c r="H26" s="93"/>
       <c r="I26" s="132"/>
       <c r="J26" s="95"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K26" s="87"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="132"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="93"/>
+      <c r="R26" s="132"/>
+      <c r="T26" s="87"/>
+      <c r="U26" s="92"/>
+      <c r="V26" s="92"/>
+      <c r="W26" s="93"/>
+      <c r="X26" s="132"/>
+      <c r="Y26" s="94"/>
+      <c r="Z26" s="93"/>
+      <c r="AA26" s="132"/>
+      <c r="AC26" s="87"/>
+      <c r="AD26" s="92"/>
+      <c r="AE26" s="92"/>
+      <c r="AF26" s="93"/>
+      <c r="AG26" s="132"/>
+      <c r="AH26" s="94"/>
+      <c r="AI26" s="93"/>
+      <c r="AJ26" s="132"/>
+      <c r="AL26" s="87"/>
+      <c r="AM26" s="92"/>
+      <c r="AN26" s="92"/>
+      <c r="AO26" s="93"/>
+      <c r="AP26" s="132"/>
+      <c r="AQ26" s="94"/>
+      <c r="AR26" s="93"/>
+      <c r="AS26" s="132"/>
+    </row>
+    <row r="27" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B27" s="75" t="s">
         <v>13</v>
       </c>
@@ -10354,32 +12202,156 @@
         <v>-19.225349999999999</v>
       </c>
       <c r="D27" s="3">
-        <f>VLOOKUP(B27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>-248.25558000000001</v>
+        <f>VLOOKUP(B27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>0</v>
       </c>
       <c r="E27" s="114">
-        <f t="shared" ref="E27:E29" si="12">C27-D27</f>
-        <v>229.03023000000002</v>
-      </c>
-      <c r="F27" s="115">
+        <f t="shared" ref="E27:E29" si="88">C27-D27</f>
+        <v>-19.225349999999999</v>
+      </c>
+      <c r="F27" s="115" t="str">
         <f>+IF(IFERROR(C27/D27-1,"-")&lt;300%,IFERROR(C27/D27-1,"-"),"n.a.")</f>
-        <v>-0.92255823615324173</v>
+        <v>n.a.</v>
       </c>
       <c r="G27" s="121">
-        <f>VLOOKUP(B27,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
-        <v>-249.99999600000004</v>
+        <f>VLOOKUP(B27,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
+        <v>-20.833333</v>
       </c>
       <c r="H27" s="114">
-        <f t="shared" ref="H27:H29" si="13">C27-G27</f>
-        <v>230.77464600000005</v>
+        <f t="shared" ref="H27:H29" si="89">C27-G27</f>
+        <v>1.6079830000000008</v>
       </c>
       <c r="I27" s="115">
         <f>+IF(IFERROR(C27/G27-1,"-")&lt;300%,IFERROR(C27/G27-1,"-"),"n.a.")</f>
-        <v>-0.92309859876957756</v>
+        <v>-7.7183185234930951E-2</v>
       </c>
       <c r="J27" s="85"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K27" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" s="3">
+        <f>GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","8.- Amortización del inmovilizado")/1000</f>
+        <v>-19.225349999999999</v>
+      </c>
+      <c r="M27" s="3">
+        <f>VLOOKUP(K27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>-194.71201000000002</v>
+      </c>
+      <c r="N27" s="114">
+        <f t="shared" ref="N27:N29" si="90">L27-M27</f>
+        <v>175.48666000000003</v>
+      </c>
+      <c r="O27" s="115">
+        <f>+IF(IFERROR(L27/M27-1,"-")&lt;300%,IFERROR(L27/M27-1,"-"),"n.a.")</f>
+        <v>-0.90126263911507054</v>
+      </c>
+      <c r="P27" s="121">
+        <f>VLOOKUP(K27,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>-20.833333</v>
+      </c>
+      <c r="Q27" s="114">
+        <f t="shared" ref="Q27:Q29" si="91">L27-P27</f>
+        <v>1.6079830000000008</v>
+      </c>
+      <c r="R27" s="115">
+        <f>+IF(IFERROR(L27/P27-1,"-")&lt;300%,IFERROR(L27/P27-1,"-"),"n.a.")</f>
+        <v>-7.7183185234930951E-2</v>
+      </c>
+      <c r="T27" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="U27" s="3">
+        <f>GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","8.- Amortización del inmovilizado")/1000</f>
+        <v>-19.225349999999999</v>
+      </c>
+      <c r="V27" s="3">
+        <f>VLOOKUP(T27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>-19.471199999999982</v>
+      </c>
+      <c r="W27" s="114">
+        <f t="shared" ref="W27:W29" si="92">U27-V27</f>
+        <v>0.24584999999998303</v>
+      </c>
+      <c r="X27" s="115">
+        <f>+IF(IFERROR(U27/V27-1,"-")&lt;300%,IFERROR(U27/V27-1,"-"),"n.a.")</f>
+        <v>-1.2626340441266204E-2</v>
+      </c>
+      <c r="Y27" s="121">
+        <f>VLOOKUP(T27,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>-20.833333</v>
+      </c>
+      <c r="Z27" s="114">
+        <f t="shared" ref="Z27:Z29" si="93">U27-Y27</f>
+        <v>1.6079830000000008</v>
+      </c>
+      <c r="AA27" s="115">
+        <f>+IF(IFERROR(U27/Y27-1,"-")&lt;300%,IFERROR(U27/Y27-1,"-"),"n.a.")</f>
+        <v>-7.7183185234930951E-2</v>
+      </c>
+      <c r="AC27" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD27" s="3">
+        <f>GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","8.- Amortización del inmovilizado")/1000</f>
+        <v>-19.225349999999999</v>
+      </c>
+      <c r="AE27" s="3">
+        <f>VLOOKUP(AC27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-34.072369999999999</v>
+      </c>
+      <c r="AF27" s="114">
+        <f t="shared" ref="AF27:AF29" si="94">AD27-AE27</f>
+        <v>14.847020000000001</v>
+      </c>
+      <c r="AG27" s="115">
+        <f>+IF(IFERROR(AD27/AE27-1,"-")&lt;300%,IFERROR(AD27/AE27-1,"-"),"n.a.")</f>
+        <v>-0.43574955308362762</v>
+      </c>
+      <c r="AH27" s="121">
+        <f>VLOOKUP(AC27,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-20.833333</v>
+      </c>
+      <c r="AI27" s="114">
+        <f t="shared" ref="AI27:AI29" si="95">AD27-AH27</f>
+        <v>1.6079830000000008</v>
+      </c>
+      <c r="AJ27" s="115">
+        <f>+IF(IFERROR(AD27/AH27-1,"-")&lt;300%,IFERROR(AD27/AH27-1,"-"),"n.a.")</f>
+        <v>-7.7183185234930951E-2</v>
+      </c>
+      <c r="AL27" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM27" s="3">
+        <f>GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","8.- Amortización del inmovilizado")/1000</f>
+        <v>-229.67474999999999</v>
+      </c>
+      <c r="AN27" s="3">
+        <f>VLOOKUP(AL27,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>-34.072369999999999</v>
+      </c>
+      <c r="AO27" s="114">
+        <f t="shared" ref="AO27:AO29" si="96">AM27-AN27</f>
+        <v>-195.60237999999998</v>
+      </c>
+      <c r="AP27" s="115" t="str">
+        <f>+IF(IFERROR(AM27/AN27-1,"-")&lt;300%,IFERROR(AM27/AN27-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AQ27" s="121">
+        <f>VLOOKUP(AL27,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>-20.833333</v>
+      </c>
+      <c r="AR27" s="114">
+        <f t="shared" ref="AR27:AR29" si="97">AM27-AQ27</f>
+        <v>-208.84141699999998</v>
+      </c>
+      <c r="AS27" s="115" t="str">
+        <f>+IF(IFERROR(AM27/AQ27-1,"-")&lt;300%,IFERROR(AM27/AQ27-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="28" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B28" s="75" t="s">
         <v>14</v>
       </c>
@@ -10388,22 +12360,22 @@
         <v>0</v>
       </c>
       <c r="D28" s="3">
-        <f>VLOOKUP(B28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+2,0)</f>
-        <v>2.3567300000000007</v>
+        <f>VLOOKUP(B28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$C$5+1,0)</f>
+        <v>-4.0640000000000003E-2</v>
       </c>
       <c r="E28" s="114">
-        <f t="shared" si="12"/>
-        <v>-2.3567300000000007</v>
+        <f t="shared" si="88"/>
+        <v>4.0640000000000003E-2</v>
       </c>
       <c r="F28" s="115" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="121">
-        <f>VLOOKUP(B28,'Budget26 sin EI'!B:O,$C$5+2,0)</f>
+        <f>VLOOKUP(B28,'Budget26 sin EI'!$B:$O,$C$5+1,0)</f>
         <v>0</v>
       </c>
       <c r="H28" s="114">
-        <f t="shared" si="13"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="I28" s="115" t="str">
@@ -10411,8 +12383,128 @@
         <v>n.a.</v>
       </c>
       <c r="J28" s="85"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K28" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="23">
+        <f>GETPIVOTDATA("oct-26 ",TABLA!$B$3,"Nivel 4","13.- Otros resultados")+GETPIVOTDATA("ago-26 ",TABLA!$B$3,"Nivel 4","11.- Deterioro y resultado por enajenaciones del inmovilizado")/1000</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <f>VLOOKUP(K28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$L$5+1,0)</f>
+        <v>0.81001000000000012</v>
+      </c>
+      <c r="N28" s="114">
+        <f t="shared" si="90"/>
+        <v>-0.81001000000000012</v>
+      </c>
+      <c r="O28" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="P28" s="121">
+        <f>VLOOKUP(K28,'Budget26 sin EI'!$B:$O,$L$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="114">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="115" t="str">
+        <f>+IF(IFERROR(L28/P28-1,"-")&lt;300%,IFERROR(L28/P28-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="T28" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="U28" s="23">
+        <f>GETPIVOTDATA("nov-26 ",TABLA!$B$3,"Nivel 4","13.- Otros resultados")+GETPIVOTDATA("ago-26 ",TABLA!$B$3,"Nivel 4","11.- Deterioro y resultado por enajenaciones del inmovilizado")/1000</f>
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <f>VLOOKUP(T28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$U$5+1,0)</f>
+        <v>4.4300000000002913E-3</v>
+      </c>
+      <c r="W28" s="114">
+        <f t="shared" si="92"/>
+        <v>-4.4300000000002913E-3</v>
+      </c>
+      <c r="X28" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y28" s="121">
+        <f>VLOOKUP(T28,'Budget26 sin EI'!$B:$O,$U$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="114">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="115" t="str">
+        <f>+IF(IFERROR(U28/Y28-1,"-")&lt;300%,IFERROR(U28/Y28-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AC28" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD28" s="23">
+        <f>GETPIVOTDATA("dic-26 ",TABLA!$B$3,"Nivel 4","13.- Otros resultados")+GETPIVOTDATA("ago-26 ",TABLA!$B$3,"Nivel 4","11.- Deterioro y resultado por enajenaciones del inmovilizado")/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <f>VLOOKUP(AC28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>0.15045</v>
+      </c>
+      <c r="AF28" s="114">
+        <f t="shared" si="94"/>
+        <v>-0.15045</v>
+      </c>
+      <c r="AG28" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH28" s="121">
+        <f>VLOOKUP(AC28,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="114">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="115" t="str">
+        <f>+IF(IFERROR(AD28/AH28-1,"-")&lt;300%,IFERROR(AD28/AH28-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+      <c r="AL28" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM28" s="23">
+        <f>GETPIVOTDATA("Total 2026 ",TABLA!$B$3,"Nivel 4","13.- Otros resultados")/1000+GETPIVOTDATA("ago-26 ",TABLA!$B$3,"Nivel 4","11.- Deterioro y resultado por enajenaciones del inmovilizado")/1000</f>
+        <v>3.9999400000000005</v>
+      </c>
+      <c r="AN28" s="3">
+        <f>VLOOKUP(AL28,'P&amp;L Mensualitzada 2025'!$A$5:$N$25,$AD$5+1,0)</f>
+        <v>0.15045</v>
+      </c>
+      <c r="AO28" s="114">
+        <f t="shared" si="96"/>
+        <v>3.8494900000000003</v>
+      </c>
+      <c r="AP28" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ28" s="121">
+        <f>VLOOKUP(AL28,'Budget26 sin EI'!$B:$O,$AD$5+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR28" s="114">
+        <f t="shared" si="97"/>
+        <v>3.9999400000000005</v>
+      </c>
+      <c r="AS28" s="115" t="str">
+        <f>+IF(IFERROR(AM28/AQ28-1,"-")&lt;300%,IFERROR(AM28/AQ28-1,"-"),"n.a.")</f>
+        <v>n.a.</v>
+      </c>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B29" s="83" t="s">
         <v>15</v>
       </c>
@@ -10422,31 +12514,155 @@
       </c>
       <c r="D29" s="112">
         <f>D24+D27+D28</f>
-        <v>5179.0873500000034</v>
+        <v>369.0702500000001</v>
       </c>
       <c r="E29" s="112">
-        <f t="shared" si="12"/>
-        <v>-5042.5755500000032</v>
+        <f t="shared" si="88"/>
+        <v>-232.55845000000011</v>
       </c>
       <c r="F29" s="127">
-        <f t="shared" si="2"/>
-        <v>-0.97364172666444793</v>
+        <f t="shared" si="6"/>
+        <v>-0.63011974007658444</v>
       </c>
       <c r="G29" s="112">
         <f>G24+G27+G28</f>
-        <v>6170.42694693049</v>
+        <v>358.89289592613977</v>
       </c>
       <c r="H29" s="112">
-        <f t="shared" si="13"/>
-        <v>-6033.9151469304898</v>
+        <f t="shared" si="89"/>
+        <v>-222.38109592613978</v>
       </c>
       <c r="I29" s="127">
         <f t="shared" si="0"/>
-        <v>-0.97787644174802058</v>
+        <v>-0.61963081033486334</v>
       </c>
       <c r="J29" s="108"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K29" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="112">
+        <f>L24+L27+L28</f>
+        <v>306.46071000000001</v>
+      </c>
+      <c r="M29" s="112">
+        <f>M24+M27+M28</f>
+        <v>-276.48445999999814</v>
+      </c>
+      <c r="N29" s="112">
+        <f t="shared" si="90"/>
+        <v>582.94516999999814</v>
+      </c>
+      <c r="O29" s="127">
+        <f t="shared" ref="O29:O30" si="98">+IF(IFERROR(L29/M29-1,"-")&lt;300%,IFERROR(L29/M29-1,"-"),"n.a.")</f>
+        <v>-2.1084192941621458</v>
+      </c>
+      <c r="P29" s="112">
+        <f>P24+P27+P28</f>
+        <v>184.40572186796439</v>
+      </c>
+      <c r="Q29" s="112">
+        <f t="shared" si="91"/>
+        <v>122.05498813203562</v>
+      </c>
+      <c r="R29" s="127">
+        <f t="shared" ref="R29:R30" si="99">+IF(IFERROR(L29/P29-1,"-")&lt;300%,IFERROR(L29/P29-1,"-"),"n.a.")</f>
+        <v>0.66188286836038479</v>
+      </c>
+      <c r="T29" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="U29" s="112">
+        <f>U24+U27+U28</f>
+        <v>512.66606999999999</v>
+      </c>
+      <c r="V29" s="112">
+        <f>V24+V27+V28</f>
+        <v>233.07388000000043</v>
+      </c>
+      <c r="W29" s="112">
+        <f t="shared" si="92"/>
+        <v>279.59218999999956</v>
+      </c>
+      <c r="X29" s="127">
+        <f t="shared" ref="X29:X30" si="100">+IF(IFERROR(U29/V29-1,"-")&lt;300%,IFERROR(U29/V29-1,"-"),"n.a.")</f>
+        <v>1.1995861140682047</v>
+      </c>
+      <c r="Y29" s="112">
+        <f>Y24+Y27+Y28</f>
+        <v>332.36609925835512</v>
+      </c>
+      <c r="Z29" s="112">
+        <f t="shared" si="93"/>
+        <v>180.29997074164487</v>
+      </c>
+      <c r="AA29" s="127">
+        <f t="shared" ref="AA29:AA30" si="101">+IF(IFERROR(U29/Y29-1,"-")&lt;300%,IFERROR(U29/Y29-1,"-"),"n.a.")</f>
+        <v>0.54247401026749698</v>
+      </c>
+      <c r="AC29" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD29" s="112">
+        <f>AD24+AD27+AD28</f>
+        <v>-34.573120000000081</v>
+      </c>
+      <c r="AE29" s="112">
+        <f>AE24+AE27+AE28</f>
+        <v>-265.73219</v>
+      </c>
+      <c r="AF29" s="112">
+        <f t="shared" si="94"/>
+        <v>231.15906999999993</v>
+      </c>
+      <c r="AG29" s="127">
+        <f t="shared" ref="AG29:AG30" si="102">+IF(IFERROR(AD29/AE29-1,"-")&lt;300%,IFERROR(AD29/AE29-1,"-"),"n.a.")</f>
+        <v>-0.86989487423409229</v>
+      </c>
+      <c r="AH29" s="112">
+        <f>AH24+AH27+AH28</f>
+        <v>-74.854859300048375</v>
+      </c>
+      <c r="AI29" s="112">
+        <f t="shared" si="95"/>
+        <v>40.281739300048294</v>
+      </c>
+      <c r="AJ29" s="127">
+        <f t="shared" ref="AJ29:AJ30" si="103">+IF(IFERROR(AD29/AH29-1,"-")&lt;300%,IFERROR(AD29/AH29-1,"-"),"n.a.")</f>
+        <v>-0.53813125395884964</v>
+      </c>
+      <c r="AL29" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM29" s="112">
+        <f>AM24+AM27+AM28</f>
+        <v>6150.5032947497075</v>
+      </c>
+      <c r="AN29" s="112">
+        <f>AN24+AN27+AN28</f>
+        <v>-265.73219</v>
+      </c>
+      <c r="AO29" s="112">
+        <f t="shared" si="96"/>
+        <v>6416.2354847497072</v>
+      </c>
+      <c r="AP29" s="127">
+        <f t="shared" ref="AP29:AP30" si="104">+IF(IFERROR(AM29/AN29-1,"-")&lt;300%,IFERROR(AM29/AN29-1,"-"),"n.a.")</f>
+        <v>-24.145495827019328</v>
+      </c>
+      <c r="AQ29" s="112">
+        <f>AQ24+AQ27+AQ28</f>
+        <v>-74.854859300048375</v>
+      </c>
+      <c r="AR29" s="112">
+        <f t="shared" si="97"/>
+        <v>6225.3581540497562</v>
+      </c>
+      <c r="AS29" s="127">
+        <f t="shared" ref="AS29:AS30" si="105">+IF(IFERROR(AM29/AQ29-1,"-")&lt;300%,IFERROR(AM29/AQ29-1,"-"),"n.a.")</f>
+        <v>-83.165718461857196</v>
+      </c>
+    </row>
+    <row r="30" spans="2:45" x14ac:dyDescent="0.35">
       <c r="B30" s="87" t="s">
         <v>16</v>
       </c>
@@ -10456,24 +12672,104 @@
       </c>
       <c r="D30" s="128">
         <f>D29/D10</f>
-        <v>0.40531127100053271</v>
+        <v>0.43826544328304312</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="134"/>
       <c r="G30" s="128">
         <f>G29/G10</f>
-        <v>0.38712760822565301</v>
+        <v>0.34960443437765643</v>
       </c>
       <c r="H30" s="90"/>
       <c r="I30" s="134"/>
       <c r="J30" s="90"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K30" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="128">
+        <f>L29/L10</f>
+        <v>0.33601121274472251</v>
+      </c>
+      <c r="M30" s="128">
+        <f>M29/M10</f>
+        <v>-0.39521297995256666</v>
+      </c>
+      <c r="N30" s="90"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="128">
+        <f>P29/P10</f>
+        <v>0.230920735986542</v>
+      </c>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="134"/>
+      <c r="T30" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="U30" s="128">
+        <f>U29/U10</f>
+        <v>0.41839301183400168</v>
+      </c>
+      <c r="V30" s="128">
+        <f>V29/V10</f>
+        <v>0.31088987748098884</v>
+      </c>
+      <c r="W30" s="90"/>
+      <c r="X30" s="134"/>
+      <c r="Y30" s="128">
+        <f>Y29/Y10</f>
+        <v>0.32260941974379403</v>
+      </c>
+      <c r="Z30" s="90"/>
+      <c r="AA30" s="134"/>
+      <c r="AC30" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD30" s="128">
+        <f>AD29/AD10</f>
+        <v>-3.0263389930131647E-2</v>
+      </c>
+      <c r="AE30" s="128">
+        <f>AE29/AE10</f>
+        <v>-1.069318967376282</v>
+      </c>
+      <c r="AF30" s="90"/>
+      <c r="AG30" s="134"/>
+      <c r="AH30" s="128">
+        <f>AH29/AH10</f>
+        <v>-0.11342596532491039</v>
+      </c>
+      <c r="AI30" s="90"/>
+      <c r="AJ30" s="134"/>
+      <c r="AL30" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM30" s="128">
+        <f>AM29/AM10</f>
+        <v>0.4051714950428002</v>
+      </c>
+      <c r="AN30" s="128">
+        <f>AN29/AN10</f>
+        <v>-1.069318967376282</v>
+      </c>
+      <c r="AO30" s="90"/>
+      <c r="AP30" s="134"/>
+      <c r="AQ30" s="128">
+        <f>AQ29/AQ10</f>
+        <v>-0.11342596532491039</v>
+      </c>
+      <c r="AR30" s="90"/>
+      <c r="AS30" s="134"/>
+    </row>
+    <row r="31" spans="2:45" x14ac:dyDescent="0.35">
       <c r="F31" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="H8:I8"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="AI8:AJ8"/>
+    <mergeCell ref="AR8:AS8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="15" orientation="landscape" r:id="rId1"/>
@@ -12523,7 +14819,7 @@
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.453125" hidden="1" customWidth="1"/>
+    <col min="4" max="9" width="11.453125" customWidth="1"/>
     <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.54296875" style="156" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="11.453125" bestFit="1" customWidth="1"/>
@@ -12586,16 +14882,16 @@
       <c r="B3" s="165" t="s">
         <v>428</v>
       </c>
-      <c r="C3" s="169" t="s">
+      <c r="C3" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="169" t="s">
+      <c r="D3" s="171" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="169" t="s">
+      <c r="E3" s="171" t="s">
         <v>317</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="172" t="s">
         <v>318</v>
       </c>
       <c r="G3" t="s">
@@ -12611,16 +14907,16 @@
         <v>438</v>
       </c>
       <c r="K3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="L3" t="s">
+        <v>470</v>
+      </c>
+      <c r="M3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N3" t="s">
         <v>479</v>
-      </c>
-      <c r="M3" t="s">
-        <v>480</v>
-      </c>
-      <c r="N3" t="s">
-        <v>492</v>
       </c>
       <c r="O3" t="s">
         <v>423</v>
@@ -12630,16 +14926,16 @@
       <c r="B4" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="170">
         <v>983817.13</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="170">
         <v>1470428.15</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="170">
         <v>1533789.4100000004</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="170">
         <v>1462146.28</v>
       </c>
       <c r="G4" s="19">
@@ -12674,16 +14970,16 @@
       <c r="B5" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="170">
         <v>-84878.079999999987</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="170">
         <v>50005.570000000007</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="170">
         <v>83552.76999999999</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="170">
         <v>8645.1999999999989</v>
       </c>
       <c r="G5" s="19">
@@ -12710,7 +15006,7 @@
       <c r="N5" s="19">
         <v>0</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="173">
         <v>-62628.5</v>
       </c>
     </row>
@@ -12718,23 +15014,23 @@
       <c r="B6" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="170">
         <v>-417787.47</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="170">
         <v>-406242.7300000001</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="170">
         <v>-469252.69999999995</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="170">
         <v>-514848.29</v>
       </c>
       <c r="G6" s="19">
         <v>-593981.23999999987</v>
       </c>
       <c r="H6" s="19">
-        <v>-653453.72</v>
+        <v>-653453.72000000009</v>
       </c>
       <c r="I6" s="19">
         <v>-519022.40000000008</v>
@@ -12743,35 +15039,35 @@
         <v>-278854.87</v>
       </c>
       <c r="K6" s="19">
-        <v>-202584.72999999998</v>
+        <v>-161790.96000000002</v>
       </c>
       <c r="L6" s="19">
-        <v>-348373.45999999996</v>
+        <v>-302101.36</v>
       </c>
       <c r="M6" s="19">
-        <v>-454951.82</v>
+        <v>-404423.28</v>
       </c>
       <c r="N6" s="19">
-        <v>-493219.49</v>
-      </c>
-      <c r="O6" s="19">
-        <v>-5352572.9199999981</v>
+        <v>-449145.32999999996</v>
+      </c>
+      <c r="O6" s="173">
+        <v>-5170904.3499999996</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="170">
         <v>-111532.01</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="170">
         <v>-142927.20000000001</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="170">
         <v>-146233.31</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="170">
         <v>-130047.67000000001</v>
       </c>
       <c r="G7" s="19">
@@ -12798,7 +15094,7 @@
       <c r="N7" s="19">
         <v>-431632.79</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="173">
         <v>-2006502.5899999999</v>
       </c>
     </row>
@@ -12806,16 +15102,16 @@
       <c r="B8" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="19">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19">
-        <v>0</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0</v>
-      </c>
-      <c r="F8" s="19">
+      <c r="C8" s="170">
+        <v>0</v>
+      </c>
+      <c r="D8" s="170">
+        <v>0</v>
+      </c>
+      <c r="E8" s="170">
+        <v>0</v>
+      </c>
+      <c r="F8" s="170">
         <v>750.75</v>
       </c>
       <c r="G8" s="19">
@@ -12842,7 +15138,7 @@
       <c r="N8" s="19">
         <v>14533.94</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="173">
         <v>114620.98</v>
       </c>
     </row>
@@ -12850,16 +15146,16 @@
       <c r="B9" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="170">
         <v>-103451.75999999995</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="170">
         <v>-62498.880000000019</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="170">
         <v>-110606.27000000002</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="170">
         <v>-107706.65</v>
       </c>
       <c r="G9" s="19">
@@ -12875,35 +15171,35 @@
         <v>-130060.6610312962</v>
       </c>
       <c r="K9" s="19">
-        <v>-139772.10999999999</v>
+        <v>-121630.06999999998</v>
       </c>
       <c r="L9" s="19">
-        <v>-160929.07999999993</v>
+        <v>-141648.47</v>
       </c>
       <c r="M9" s="19">
-        <v>-167978.15999999995</v>
+        <v>-149836.12</v>
       </c>
       <c r="N9" s="19">
-        <v>-309653.01000000024</v>
-      </c>
-      <c r="O9" s="19">
-        <v>-1752114.1652502934</v>
+        <v>-291510.97000000026</v>
+      </c>
+      <c r="O9" s="173">
+        <v>-1678407.4352502942</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="19">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19">
+      <c r="C10" s="170">
+        <v>0</v>
+      </c>
+      <c r="D10" s="170">
+        <v>0</v>
+      </c>
+      <c r="E10" s="170">
         <v>2000</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="170">
         <v>0</v>
       </c>
       <c r="G10" s="19">
@@ -12930,7 +15226,7 @@
       <c r="N10" s="19">
         <v>0</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="173">
         <v>2000</v>
       </c>
     </row>
@@ -12938,16 +15234,16 @@
       <c r="B11" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="170">
         <v>-19132.87</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="170">
         <v>-19132.87</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="170">
         <v>-18903.55</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="170">
         <v>-18903.55</v>
       </c>
       <c r="G11" s="19">
@@ -12974,7 +15270,7 @@
       <c r="N11" s="19">
         <v>-19225.349999999999</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="173">
         <v>-229674.75</v>
       </c>
     </row>
@@ -12982,16 +15278,16 @@
       <c r="B12" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="170">
         <v>3065.27</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="170">
         <v>0.02</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="170">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="170">
         <v>1024.26</v>
       </c>
       <c r="G12" s="19">
@@ -13018,7 +15314,7 @@
       <c r="N12" s="19">
         <v>0</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="173">
         <v>3999.9400000000005</v>
       </c>
     </row>
@@ -13026,16 +15322,16 @@
       <c r="B13" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="170">
         <v>-52.82</v>
       </c>
-      <c r="D13" s="19">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19">
+      <c r="D13" s="170">
+        <v>0</v>
+      </c>
+      <c r="E13" s="170">
         <v>-79.37</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="170">
         <v>-24483.469999999998</v>
       </c>
       <c r="G13" s="19">
@@ -13051,35 +15347,35 @@
         <v>-19768.43</v>
       </c>
       <c r="K13" s="19">
-        <v>-13012.259999999998</v>
+        <v>-12975.21</v>
       </c>
       <c r="L13" s="19">
-        <v>-25116.059999999998</v>
+        <v>-24579.01</v>
       </c>
       <c r="M13" s="19">
-        <v>-33879.72</v>
+        <v>-33042.67</v>
       </c>
       <c r="N13" s="19">
-        <v>-36711.270000000004</v>
-      </c>
-      <c r="O13" s="19">
-        <v>-302856.55000000005</v>
+        <v>-35674.22</v>
+      </c>
+      <c r="O13" s="173">
+        <v>-300408.35000000003</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="19">
-        <v>0</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="C14" s="170">
+        <v>0</v>
+      </c>
+      <c r="D14" s="170">
         <v>78.790000000000006</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="170">
         <v>15.51</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="170">
         <v>0</v>
       </c>
       <c r="G14" s="19">
@@ -13095,35 +15391,35 @@
         <v>0</v>
       </c>
       <c r="K14" s="19">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M14" s="19">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N14" s="19">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="O14" s="19">
-        <v>7844.51</v>
+        <v>5244.51</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="C15" s="19">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="C15" s="170">
+        <v>0</v>
+      </c>
+      <c r="D15" s="170">
+        <v>0</v>
+      </c>
+      <c r="E15" s="170">
+        <v>0</v>
+      </c>
+      <c r="F15" s="170">
         <v>0</v>
       </c>
       <c r="G15" s="19">
@@ -13148,33 +15444,33 @@
         <v>0</v>
       </c>
       <c r="N15" s="19">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="O15" s="19">
-        <v>6995.93</v>
+        <v>4495.93</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="170">
         <v>250047.3900000001</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="170">
         <v>889710.84999999986</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="170">
         <v>874282.35000000033</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="170">
         <v>676576.85999999987</v>
       </c>
       <c r="G16" s="19">
         <v>1013450.7200000003</v>
       </c>
       <c r="H16" s="19">
-        <v>830198.85000000009</v>
+        <v>830198.84999999986</v>
       </c>
       <c r="I16" s="19">
         <v>410468.30578100268</v>
@@ -13183,19 +15479,19 @@
         <v>205726.73896870381</v>
       </c>
       <c r="K16" s="19">
-        <v>-38457.299999999974</v>
+        <v>20115.559999999998</v>
       </c>
       <c r="L16" s="19">
-        <v>216391.94000000006</v>
+        <v>281881.69999999995</v>
       </c>
       <c r="M16" s="19">
-        <v>410915.77</v>
+        <v>479623.39999999997</v>
       </c>
       <c r="N16" s="19">
-        <v>-130200.59000000008</v>
+        <v>-70247.340000000084</v>
       </c>
       <c r="O16" s="19">
-        <v>5609111.8847497106</v>
+        <v>5861835.3847497087</v>
       </c>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.35">
@@ -13224,7 +15520,7 @@
       </c>
       <c r="H17" s="19">
         <f t="shared" si="0"/>
-        <v>921594.8</v>
+        <v>921594.79999999981</v>
       </c>
       <c r="I17" s="19">
         <f t="shared" si="0"/>
@@ -13236,23 +15532,23 @@
       </c>
       <c r="K17" s="19">
         <f t="shared" si="0"/>
-        <v>-6619.6899999999732</v>
+        <v>52316.119999999995</v>
       </c>
       <c r="L17" s="19">
         <f t="shared" si="0"/>
-        <v>260133.35000000006</v>
+        <v>325686.05999999994</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="0"/>
-        <v>463220.83999999997</v>
+        <v>531891.41999999993</v>
       </c>
       <c r="N17" s="19">
         <f t="shared" si="0"/>
-        <v>-77563.970000000088</v>
+        <v>-15347.770000000077</v>
       </c>
       <c r="O17" s="19">
         <f t="shared" si="0"/>
-        <v>6120802.8047497105</v>
+        <v>6376178.1047497084</v>
       </c>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
@@ -13295,7 +15591,7 @@
       </c>
       <c r="H18" s="167">
         <f t="shared" si="1"/>
-        <v>0.4696594439693097</v>
+        <v>0.46965944396930959</v>
       </c>
       <c r="I18" s="167">
         <f t="shared" si="1"/>
@@ -13307,23 +15603,23 @@
       </c>
       <c r="K18" s="167">
         <f>K17/K4</f>
-        <v>-1.3702986567090777E-2</v>
+        <v>0.10829617241929938</v>
       </c>
       <c r="L18" s="167">
         <f t="shared" ref="L18:O18" si="2">L17/L4</f>
-        <v>0.28521673270562931</v>
+        <v>0.35709036892412876</v>
       </c>
       <c r="M18" s="167">
         <f t="shared" si="2"/>
-        <v>0.37804015856145146</v>
+        <v>0.43408305367754085</v>
       </c>
       <c r="N18" s="167">
         <f t="shared" si="2"/>
-        <v>-6.7895193394146389E-2</v>
+        <v>-1.3434585830494263E-2</v>
       </c>
       <c r="O18" s="167">
         <f t="shared" si="2"/>
-        <v>0.40321494102435507</v>
+        <v>0.42003808331684506</v>
       </c>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
@@ -13385,21 +15681,21 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="30.26953125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="29.1796875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="51.81640625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" customWidth="1"/>
+    <col min="5" max="5" width="30.26953125" customWidth="1"/>
+    <col min="6" max="6" width="29.1796875" customWidth="1"/>
+    <col min="7" max="7" width="51.81640625" customWidth="1"/>
     <col min="8" max="8" width="58.54296875" customWidth="1"/>
     <col min="9" max="9" width="64.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.1796875" hidden="1" customWidth="1"/>
-    <col min="12" max="14" width="12.1796875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7265625" style="156" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.453125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="21.81640625" style="156" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="21.81640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="30.26953125" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" customWidth="1"/>
+    <col min="12" max="14" width="12.1796875" customWidth="1"/>
+    <col min="15" max="15" width="15.7265625" style="156" customWidth="1"/>
+    <col min="16" max="16" width="14.453125" customWidth="1"/>
+    <col min="17" max="17" width="21.81640625" style="156" customWidth="1"/>
+    <col min="18" max="18" width="21.81640625" customWidth="1"/>
     <col min="19" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.26953125" bestFit="1" customWidth="1"/>
@@ -13441,23 +15737,23 @@
       </c>
       <c r="S2" s="19">
         <f t="shared" ref="S2:V2" si="0">SUBTOTAL(9,S4:S215)</f>
-        <v>-38457.299999999952</v>
+        <v>20115.560000000092</v>
       </c>
       <c r="T2" s="19">
         <f t="shared" si="0"/>
-        <v>216391.93999999954</v>
+        <v>281881.6999999996</v>
       </c>
       <c r="U2" s="19">
         <f t="shared" si="0"/>
-        <v>410915.7699999999</v>
+        <v>479623.40000000055</v>
       </c>
       <c r="V2" s="19">
         <f t="shared" si="0"/>
-        <v>-130200.58999999991</v>
+        <v>-70247.340000000098</v>
       </c>
       <c r="W2" s="19">
         <f>SUBTOTAL(9,W4:W2036)</f>
-        <v>5609111.8847497134</v>
+        <v>5861835.3847497106</v>
       </c>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.35">
@@ -13596,7 +15892,7 @@
         <v>15420283.770000003</v>
       </c>
       <c r="X4" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.35">
@@ -14506,7 +16802,7 @@
         <v>-333000</v>
       </c>
       <c r="X17" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.35">
@@ -14917,22 +17213,22 @@
         <v>-189242.44</v>
       </c>
       <c r="S23" s="19">
-        <v>-129824.18</v>
+        <v>-124233.67</v>
       </c>
       <c r="T23" s="19">
-        <v>-245926.61</v>
+        <v>-235336.47</v>
       </c>
       <c r="U23" s="19">
-        <v>-330610.32</v>
+        <v>-316373.51</v>
       </c>
       <c r="V23" s="19">
-        <v>-356940.43</v>
+        <v>-341569.79</v>
       </c>
       <c r="W23" s="19">
-        <v>-4111061.0299999993</v>
+        <v>-4065272.9299999997</v>
       </c>
       <c r="X23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.35">
@@ -14979,7 +17275,7 @@
         <v>-30193.149999999991</v>
       </c>
       <c r="P24" s="19">
-        <v>-89165.98000000001</v>
+        <v>-119472.15</v>
       </c>
       <c r="Q24" s="19">
         <v>-145291.04999999999</v>
@@ -14988,22 +17284,22 @@
         <v>-8606.0399999999936</v>
       </c>
       <c r="S24" s="19">
-        <v>-25070.99</v>
+        <v>-25894.98</v>
       </c>
       <c r="T24" s="19">
-        <v>-47492.1</v>
+        <v>-49053</v>
       </c>
       <c r="U24" s="19">
-        <v>-63845.79</v>
+        <v>-65944.179999999993</v>
       </c>
       <c r="V24" s="19">
-        <v>-68930.53</v>
+        <v>-71196.03</v>
       </c>
       <c r="W24" s="19">
-        <v>-793861.58</v>
+        <v>-830916.5299999998</v>
       </c>
       <c r="X24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.35">
@@ -15039,7 +17335,7 @@
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
       <c r="P25" s="19">
-        <v>-30306.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="19">
         <v>0</v>
@@ -15048,22 +17344,22 @@
         <v>0</v>
       </c>
       <c r="S25" s="19">
-        <v>-30306.17</v>
+        <v>0</v>
       </c>
       <c r="T25" s="19">
-        <v>-30306.17</v>
+        <v>0</v>
       </c>
       <c r="U25" s="19">
-        <v>-30306.17</v>
+        <v>0</v>
       </c>
       <c r="V25" s="19">
-        <v>-30306.17</v>
+        <v>0</v>
       </c>
       <c r="W25" s="19">
-        <v>-151530.84999999998</v>
+        <v>0</v>
       </c>
       <c r="X25" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.35">
@@ -15119,19 +17415,19 @@
         <v>-2886.68</v>
       </c>
       <c r="S26" s="19">
-        <v>-2744.02</v>
+        <v>-2625.86</v>
       </c>
       <c r="T26" s="19">
-        <v>-5198</v>
+        <v>-4974.16</v>
       </c>
       <c r="U26" s="19">
-        <v>-6987.91</v>
+        <v>-6687</v>
       </c>
       <c r="V26" s="19">
-        <v>-7544.44</v>
+        <v>-7219.56</v>
       </c>
       <c r="W26" s="19">
-        <v>-86934.27</v>
+        <v>-85966.48</v>
       </c>
       <c r="X26" t="s">
         <v>485</v>
@@ -15190,19 +17486,19 @@
         <v>-4331.6000000000004</v>
       </c>
       <c r="S27" s="19">
-        <v>-2854.55</v>
+        <v>-2731.63</v>
       </c>
       <c r="T27" s="19">
-        <v>-5407.38</v>
+        <v>-5174.53</v>
       </c>
       <c r="U27" s="19">
-        <v>-7269.39</v>
+        <v>-6956.35</v>
       </c>
       <c r="V27" s="19">
-        <v>-7848.33</v>
+        <v>-7510.36</v>
       </c>
       <c r="W27" s="19">
-        <v>-90442.1</v>
+        <v>-89435.32</v>
       </c>
       <c r="X27" t="s">
         <v>486</v>
@@ -15418,7 +17714,7 @@
         <v>-33930.639999999999</v>
       </c>
       <c r="X30" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.35">
@@ -15971,22 +18267,22 @@
         <v>-6131.3100000000013</v>
       </c>
       <c r="S38" s="19">
-        <v>-5480</v>
+        <v>0</v>
       </c>
       <c r="T38" s="19">
-        <v>-6480</v>
+        <v>0</v>
       </c>
       <c r="U38" s="19">
-        <v>-7470</v>
+        <v>0</v>
       </c>
       <c r="V38" s="19">
         <v>-7970</v>
       </c>
       <c r="W38" s="19">
-        <v>-85188.09</v>
+        <v>-65758.09</v>
       </c>
       <c r="X38" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.35">
@@ -16270,7 +18566,7 @@
         <v>-1672192.3699999999</v>
       </c>
       <c r="X42" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.35">
@@ -16341,7 +18637,7 @@
         <v>-331599.21999999997</v>
       </c>
       <c r="X43" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.35">
@@ -16980,7 +19276,7 @@
         <v>-2711</v>
       </c>
       <c r="X52" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.35">
@@ -17406,7 +19702,7 @@
         <v>-2902.48</v>
       </c>
       <c r="X58" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.35">
@@ -17477,7 +19773,7 @@
         <v>-8938.4600000000009</v>
       </c>
       <c r="X59" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.35">
@@ -17548,7 +19844,7 @@
         <v>-14750.280000000002</v>
       </c>
       <c r="X60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.35">
@@ -17619,7 +19915,7 @@
         <v>-2304</v>
       </c>
       <c r="X61" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.35">
@@ -17667,22 +19963,22 @@
         <v>0</v>
       </c>
       <c r="S62" s="19">
-        <v>-2695.12</v>
+        <v>0</v>
       </c>
       <c r="T62" s="19">
-        <v>-2695.12</v>
+        <v>0</v>
       </c>
       <c r="U62" s="19">
-        <v>-2695.12</v>
+        <v>0</v>
       </c>
       <c r="V62" s="19">
-        <v>-2695.12</v>
+        <v>0</v>
       </c>
       <c r="W62" s="19">
-        <v>-32341.439999999995</v>
+        <v>-21560.959999999999</v>
       </c>
       <c r="X62" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.35">
@@ -17824,7 +20120,7 @@
         <v>-2168.7599999999998</v>
       </c>
       <c r="X64" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.35">
@@ -17966,7 +20262,7 @@
         <v>-2219.8200000000002</v>
       </c>
       <c r="X66" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.35">
@@ -18108,7 +20404,7 @@
         <v>-4056</v>
       </c>
       <c r="X68" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="69" spans="2:24" x14ac:dyDescent="0.35">
@@ -18179,7 +20475,7 @@
         <v>-4701.5999999999995</v>
       </c>
       <c r="X69" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="70" spans="2:24" x14ac:dyDescent="0.35">
@@ -18250,7 +20546,7 @@
         <v>-3450.5699999999997</v>
       </c>
       <c r="X70" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" spans="2:24" x14ac:dyDescent="0.35">
@@ -18321,7 +20617,7 @@
         <v>-5695.8200000000015</v>
       </c>
       <c r="X71" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="72" spans="2:24" x14ac:dyDescent="0.35">
@@ -18534,7 +20830,7 @@
         <v>-2514.2800000000002</v>
       </c>
       <c r="X74" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.35">
@@ -18605,7 +20901,7 @@
         <v>-2517.0400000000004</v>
       </c>
       <c r="X75" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.35">
@@ -18676,7 +20972,7 @@
         <v>-3858.8900000000003</v>
       </c>
       <c r="X76" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.35">
@@ -18747,7 +21043,7 @@
         <v>-14020.760000000002</v>
       </c>
       <c r="X77" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.35">
@@ -18818,7 +21114,7 @@
         <v>-12043.329999999998</v>
       </c>
       <c r="X78" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.35">
@@ -18889,7 +21185,7 @@
         <v>-7744.09</v>
       </c>
       <c r="X79" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.35">
@@ -18960,7 +21256,7 @@
         <v>-19200</v>
       </c>
       <c r="X80" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.35">
@@ -19031,7 +21327,7 @@
         <v>-13119.71</v>
       </c>
       <c r="X81" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.35">
@@ -19102,7 +21398,7 @@
         <v>-5422</v>
       </c>
       <c r="X82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.35">
@@ -19158,22 +21454,22 @@
         <v>0</v>
       </c>
       <c r="S83" s="19">
-        <v>-748.65</v>
+        <v>-716.42</v>
       </c>
       <c r="T83" s="19">
-        <v>-748.65</v>
+        <v>-716.42</v>
       </c>
       <c r="U83" s="19">
-        <v>-748.65</v>
+        <v>-716.42</v>
       </c>
       <c r="V83" s="19">
-        <v>-748.65</v>
+        <v>-716.42</v>
       </c>
       <c r="W83" s="19">
-        <v>-6576.6799999999985</v>
+        <v>-6447.76</v>
       </c>
       <c r="X83" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.35">
@@ -19229,22 +21525,22 @@
         <v>-115.48</v>
       </c>
       <c r="S84" s="19">
-        <v>-731.87</v>
+        <v>-700.36</v>
       </c>
       <c r="T84" s="19">
-        <v>-731.87</v>
+        <v>-700.36</v>
       </c>
       <c r="U84" s="19">
-        <v>-731.87</v>
+        <v>-700.36</v>
       </c>
       <c r="V84" s="19">
-        <v>-731.87</v>
+        <v>-700.36</v>
       </c>
       <c r="W84" s="19">
-        <v>-5028.55</v>
+        <v>-4902.51</v>
       </c>
       <c r="X84" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.35">
@@ -19300,22 +21596,22 @@
         <v>0</v>
       </c>
       <c r="S85" s="19">
-        <v>-122.19</v>
+        <v>-116.92</v>
       </c>
       <c r="T85" s="19">
-        <v>-122.19</v>
+        <v>-116.92</v>
       </c>
       <c r="U85" s="19">
-        <v>-122.19</v>
+        <v>-116.92</v>
       </c>
       <c r="V85" s="19">
-        <v>-122.19</v>
+        <v>-116.92</v>
       </c>
       <c r="W85" s="19">
-        <v>-956.46</v>
+        <v>-935.37999999999988</v>
       </c>
       <c r="X85" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.35">
@@ -19371,22 +21667,22 @@
         <v>0</v>
       </c>
       <c r="S86" s="19">
-        <v>-1425.85</v>
+        <v>-1364.45</v>
       </c>
       <c r="T86" s="19">
-        <v>-1425.85</v>
+        <v>-1364.45</v>
       </c>
       <c r="U86" s="19">
-        <v>-1425.85</v>
+        <v>-1364.45</v>
       </c>
       <c r="V86" s="19">
-        <v>-1425.85</v>
+        <v>-1364.45</v>
       </c>
       <c r="W86" s="19">
-        <v>-12525.640000000001</v>
+        <v>-12280.04</v>
       </c>
       <c r="X86" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.35">
@@ -19442,22 +21738,22 @@
         <v>0</v>
       </c>
       <c r="S87" s="19">
-        <v>-249.63</v>
+        <v>-238.88</v>
       </c>
       <c r="T87" s="19">
-        <v>-249.63</v>
+        <v>-238.88</v>
       </c>
       <c r="U87" s="19">
-        <v>-249.63</v>
+        <v>-238.88</v>
       </c>
       <c r="V87" s="19">
-        <v>-249.63</v>
+        <v>-238.88</v>
       </c>
       <c r="W87" s="19">
-        <v>-1237.4000000000001</v>
+        <v>-1194.4000000000001</v>
       </c>
       <c r="X87" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.35">
@@ -19513,22 +21809,22 @@
         <v>0</v>
       </c>
       <c r="S88" s="19">
-        <v>-515.01</v>
+        <v>-492.83</v>
       </c>
       <c r="T88" s="19">
-        <v>-515.01</v>
+        <v>-492.83</v>
       </c>
       <c r="U88" s="19">
-        <v>-515.01</v>
+        <v>-492.83</v>
       </c>
       <c r="V88" s="19">
-        <v>-515.01</v>
+        <v>-492.83</v>
       </c>
       <c r="W88" s="19">
-        <v>-3045.7</v>
+        <v>-2956.98</v>
       </c>
       <c r="X88" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.35">
@@ -19599,7 +21895,7 @@
         <v>0</v>
       </c>
       <c r="X89" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.35">
@@ -19655,22 +21951,22 @@
         <v>-977.98</v>
       </c>
       <c r="S90" s="19">
-        <v>-935.11</v>
+        <v>-894.85</v>
       </c>
       <c r="T90" s="19">
-        <v>-935.11</v>
+        <v>-894.85</v>
       </c>
       <c r="U90" s="19">
-        <v>-935.11</v>
+        <v>-894.85</v>
       </c>
       <c r="V90" s="19">
-        <v>-935.11</v>
+        <v>-894.85</v>
       </c>
       <c r="W90" s="19">
-        <v>-9109.5199999999986</v>
+        <v>-8948.4800000000014</v>
       </c>
       <c r="X90" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.35">
@@ -19726,22 +22022,22 @@
         <v>0</v>
       </c>
       <c r="S91" s="19">
-        <v>-1472.45</v>
+        <v>-1409.04</v>
       </c>
       <c r="T91" s="19">
-        <v>-1472.45</v>
+        <v>-1409.04</v>
       </c>
       <c r="U91" s="19">
-        <v>-1472.45</v>
+        <v>-1409.04</v>
       </c>
       <c r="V91" s="19">
-        <v>-1472.45</v>
+        <v>-1409.04</v>
       </c>
       <c r="W91" s="19">
-        <v>-7298.8399999999992</v>
+        <v>-7045.2</v>
       </c>
       <c r="X91" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.35">
@@ -19812,7 +22108,7 @@
         <v>0</v>
       </c>
       <c r="X92" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.35">
@@ -19868,22 +22164,22 @@
         <v>-1983.69</v>
       </c>
       <c r="S93" s="19">
-        <v>-2527.63</v>
+        <v>-2418.7800000000002</v>
       </c>
       <c r="T93" s="19">
-        <v>-2527.63</v>
+        <v>-2418.7800000000002</v>
       </c>
       <c r="U93" s="19">
-        <v>-2527.63</v>
+        <v>-2418.7800000000002</v>
       </c>
       <c r="V93" s="19">
-        <v>-2527.63</v>
+        <v>-2418.7800000000002</v>
       </c>
       <c r="W93" s="19">
-        <v>-27041.980000000003</v>
+        <v>-26606.579999999994</v>
       </c>
       <c r="X93" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" spans="2:24" x14ac:dyDescent="0.35">
@@ -19939,22 +22235,22 @@
         <v>-5848.16</v>
       </c>
       <c r="S94" s="19">
-        <v>-4187.1400000000003</v>
+        <v>-4006.83</v>
       </c>
       <c r="T94" s="19">
-        <v>-4187.1400000000003</v>
+        <v>-4006.83</v>
       </c>
       <c r="U94" s="19">
-        <v>-4187.1400000000003</v>
+        <v>-4006.83</v>
       </c>
       <c r="V94" s="19">
-        <v>-4187.1400000000003</v>
+        <v>-4006.83</v>
       </c>
       <c r="W94" s="19">
-        <v>-32775.89</v>
+        <v>-32054.65</v>
       </c>
       <c r="X94" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95" spans="2:24" x14ac:dyDescent="0.35">
@@ -20010,22 +22306,22 @@
         <v>-11965.55</v>
       </c>
       <c r="S95" s="19">
-        <v>-5939.08</v>
+        <v>-5683.33</v>
       </c>
       <c r="T95" s="19">
-        <v>-5939.08</v>
+        <v>-5683.33</v>
       </c>
       <c r="U95" s="19">
-        <v>-5939.08</v>
+        <v>-5683.33</v>
       </c>
       <c r="V95" s="19">
-        <v>-5939.08</v>
+        <v>-5683.33</v>
       </c>
       <c r="W95" s="19">
-        <v>-40806.310000000005</v>
+        <v>-39783.310000000005</v>
       </c>
       <c r="X95" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="2:24" x14ac:dyDescent="0.35">
@@ -20081,22 +22377,22 @@
         <v>-288.39</v>
       </c>
       <c r="S96" s="19">
-        <v>-915.9</v>
+        <v>-876.46</v>
       </c>
       <c r="T96" s="19">
-        <v>-915.9</v>
+        <v>-876.46</v>
       </c>
       <c r="U96" s="19">
-        <v>-915.9</v>
+        <v>-876.46</v>
       </c>
       <c r="V96" s="19">
-        <v>-915.9</v>
+        <v>-876.46</v>
       </c>
       <c r="W96" s="19">
-        <v>-8922.3499999999985</v>
+        <v>-8764.59</v>
       </c>
       <c r="X96" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="97" spans="2:24" x14ac:dyDescent="0.35">
@@ -20152,22 +22448,22 @@
         <v>-108.17</v>
       </c>
       <c r="S97" s="19">
-        <v>-788.2</v>
+        <v>-754.26</v>
       </c>
       <c r="T97" s="19">
-        <v>-788.2</v>
+        <v>-754.26</v>
       </c>
       <c r="U97" s="19">
-        <v>-788.2</v>
+        <v>-754.26</v>
       </c>
       <c r="V97" s="19">
-        <v>-788.2</v>
+        <v>-754.26</v>
       </c>
       <c r="W97" s="19">
-        <v>-7678.37</v>
+        <v>-7542.6100000000015</v>
       </c>
       <c r="X97" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="2:24" x14ac:dyDescent="0.35">
@@ -20223,22 +22519,22 @@
         <v>0</v>
       </c>
       <c r="S98" s="19">
-        <v>-121.44</v>
+        <v>-116.21</v>
       </c>
       <c r="T98" s="19">
-        <v>-121.44</v>
+        <v>-116.21</v>
       </c>
       <c r="U98" s="19">
-        <v>-121.44</v>
+        <v>-116.21</v>
       </c>
       <c r="V98" s="19">
-        <v>-121.44</v>
+        <v>-116.21</v>
       </c>
       <c r="W98" s="19">
-        <v>-834.40000000000009</v>
+        <v>-813.48</v>
       </c>
       <c r="X98" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
     </row>
     <row r="99" spans="2:24" x14ac:dyDescent="0.35">
@@ -20309,7 +22605,7 @@
         <v>-74612.31</v>
       </c>
       <c r="X99" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="100" spans="2:24" x14ac:dyDescent="0.35">
@@ -20380,7 +22676,7 @@
         <v>-33586.57</v>
       </c>
       <c r="X100" t="s">
-        <v>454</v>
+        <v>490</v>
       </c>
     </row>
     <row r="101" spans="2:24" x14ac:dyDescent="0.35">
@@ -20451,7 +22747,7 @@
         <v>-23694.510000000002</v>
       </c>
       <c r="X101" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="102" spans="2:24" x14ac:dyDescent="0.35">
@@ -20522,7 +22818,7 @@
         <v>-8897.9800000000014</v>
       </c>
       <c r="X102" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" spans="2:24" x14ac:dyDescent="0.35">
@@ -20593,7 +22889,7 @@
         <v>-7326.6799999999985</v>
       </c>
       <c r="X103" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="104" spans="2:24" x14ac:dyDescent="0.35">
@@ -20664,7 +22960,7 @@
         <v>-52289.990000000005</v>
       </c>
       <c r="X104" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="105" spans="2:24" x14ac:dyDescent="0.35">
@@ -20735,7 +23031,7 @@
         <v>-54130.6</v>
       </c>
       <c r="X105" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="106" spans="2:24" x14ac:dyDescent="0.35">
@@ -20806,7 +23102,7 @@
         <v>-214771.72999999998</v>
       </c>
       <c r="X106" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="107" spans="2:24" x14ac:dyDescent="0.35">
@@ -20854,22 +23150,22 @@
         <v>0</v>
       </c>
       <c r="S107" s="19">
+        <v>0</v>
+      </c>
+      <c r="T107" s="19">
+        <v>0</v>
+      </c>
+      <c r="U107" s="19">
+        <v>0</v>
+      </c>
+      <c r="V107" s="19">
+        <v>0</v>
+      </c>
+      <c r="W107" s="19">
         <v>-3398.55</v>
       </c>
-      <c r="T107" s="19">
-        <v>-3398.55</v>
-      </c>
-      <c r="U107" s="19">
-        <v>-3398.55</v>
-      </c>
-      <c r="V107" s="19">
-        <v>-3398.55</v>
-      </c>
-      <c r="W107" s="19">
-        <v>-16992.75</v>
-      </c>
       <c r="X107" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
     </row>
     <row r="108" spans="2:24" x14ac:dyDescent="0.35">
@@ -21011,7 +23307,7 @@
         <v>-755.12</v>
       </c>
       <c r="X109" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="2:24" x14ac:dyDescent="0.35">
@@ -21082,7 +23378,7 @@
         <v>0</v>
       </c>
       <c r="X110" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="2:24" x14ac:dyDescent="0.35">
@@ -21153,7 +23449,7 @@
         <v>-1912.1</v>
       </c>
       <c r="X111" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="112" spans="2:24" x14ac:dyDescent="0.35">
@@ -21224,7 +23520,7 @@
         <v>-808.97</v>
       </c>
       <c r="X112" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="113" spans="2:24" x14ac:dyDescent="0.35">
@@ -21295,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="X113" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114" spans="2:24" x14ac:dyDescent="0.35">
@@ -21358,7 +23654,7 @@
         <v>-83.47</v>
       </c>
       <c r="X114" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="115" spans="2:24" x14ac:dyDescent="0.35">
@@ -21418,7 +23714,7 @@
         <v>-267.75</v>
       </c>
       <c r="X115" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="2:24" x14ac:dyDescent="0.35">
@@ -21478,7 +23774,7 @@
         <v>-2450</v>
       </c>
       <c r="X116" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="117" spans="2:24" x14ac:dyDescent="0.35">
@@ -21549,7 +23845,7 @@
         <v>-566.14</v>
       </c>
       <c r="X117" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="118" spans="2:24" x14ac:dyDescent="0.35">
@@ -21620,7 +23916,7 @@
         <v>-543.35</v>
       </c>
       <c r="X118" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" spans="2:24" x14ac:dyDescent="0.35">
@@ -21691,7 +23987,7 @@
         <v>-543.4</v>
       </c>
       <c r="X119" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="120" spans="2:24" x14ac:dyDescent="0.35">
@@ -21762,7 +24058,7 @@
         <v>-1190</v>
       </c>
       <c r="X120" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="2:24" x14ac:dyDescent="0.35">
@@ -21818,7 +24114,7 @@
         <v>-24349.75</v>
       </c>
       <c r="X121" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="122" spans="2:24" x14ac:dyDescent="0.35">
@@ -21889,7 +24185,7 @@
         <v>-543.35</v>
       </c>
       <c r="X122" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="2:24" x14ac:dyDescent="0.35">
@@ -21960,7 +24256,7 @@
         <v>-513</v>
       </c>
       <c r="X123" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="2:24" x14ac:dyDescent="0.35">
@@ -22031,7 +24327,7 @@
         <v>-10164.06</v>
       </c>
       <c r="X124" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="125" spans="2:24" x14ac:dyDescent="0.35">
@@ -22102,7 +24398,7 @@
         <v>-513</v>
       </c>
       <c r="X125" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="126" spans="2:24" x14ac:dyDescent="0.35">
@@ -22173,7 +24469,7 @@
         <v>-596.47</v>
       </c>
       <c r="X126" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="127" spans="2:24" x14ac:dyDescent="0.35">
@@ -22244,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="X127" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" spans="2:24" x14ac:dyDescent="0.35">
@@ -22315,7 +24611,7 @@
         <v>-159898.70000000001</v>
       </c>
       <c r="X128" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
     </row>
     <row r="129" spans="2:24" x14ac:dyDescent="0.35">
@@ -22386,7 +24682,7 @@
         <v>-114577.38999999998</v>
       </c>
       <c r="X129" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="130" spans="2:24" x14ac:dyDescent="0.35">
@@ -22457,7 +24753,7 @@
         <v>-69093.88</v>
       </c>
       <c r="X130" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="131" spans="2:24" x14ac:dyDescent="0.35">
@@ -22528,7 +24824,7 @@
         <v>-59421.44999999999</v>
       </c>
       <c r="X131" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="132" spans="2:24" x14ac:dyDescent="0.35">
@@ -22599,7 +24895,7 @@
         <v>-5914.5700000000006</v>
       </c>
       <c r="X132" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="133" spans="2:24" x14ac:dyDescent="0.35">
@@ -22670,7 +24966,7 @@
         <v>-9723.2900000000009</v>
       </c>
       <c r="X133" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="2:24" x14ac:dyDescent="0.35">
@@ -22812,7 +25108,7 @@
         <v>-940.84999999999991</v>
       </c>
       <c r="X135" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="136" spans="2:24" x14ac:dyDescent="0.35">
@@ -22883,7 +25179,7 @@
         <v>-973.19999999999993</v>
       </c>
       <c r="X136" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="137" spans="2:24" x14ac:dyDescent="0.35">
@@ -22954,7 +25250,7 @@
         <v>-19689.54</v>
       </c>
       <c r="X137" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="2:24" x14ac:dyDescent="0.35">
@@ -23025,7 +25321,7 @@
         <v>-26781.119999999999</v>
       </c>
       <c r="X138" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="139" spans="2:24" x14ac:dyDescent="0.35">
@@ -23167,7 +25463,7 @@
         <v>-588.23</v>
       </c>
       <c r="X140" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="141" spans="2:24" x14ac:dyDescent="0.35">
@@ -23238,7 +25534,7 @@
         <v>-2054.0100000000002</v>
       </c>
       <c r="X141" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="142" spans="2:24" x14ac:dyDescent="0.35">
@@ -23309,7 +25605,7 @@
         <v>-9733.0399999999991</v>
       </c>
       <c r="X142" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="143" spans="2:24" x14ac:dyDescent="0.35">
@@ -23451,7 +25747,7 @@
         <v>-1180.3</v>
       </c>
       <c r="X144" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145" spans="2:24" x14ac:dyDescent="0.35">
@@ -23522,7 +25818,7 @@
         <v>-2238.5</v>
       </c>
       <c r="X145" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="146" spans="2:24" x14ac:dyDescent="0.35">
@@ -23593,7 +25889,7 @@
         <v>-643.11000000000013</v>
       </c>
       <c r="X146" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="2:24" x14ac:dyDescent="0.35">
@@ -23664,7 +25960,7 @@
         <v>-1696.53</v>
       </c>
       <c r="X147" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148" spans="2:24" x14ac:dyDescent="0.35">
@@ -23720,22 +26016,22 @@
         <v>0</v>
       </c>
       <c r="S148" s="19">
-        <v>-2277.14</v>
+        <v>0</v>
       </c>
       <c r="T148" s="19">
-        <v>-3415.71</v>
+        <v>0</v>
       </c>
       <c r="U148" s="19">
-        <v>-2277.14</v>
+        <v>0</v>
       </c>
       <c r="V148" s="19">
-        <v>-2277.14</v>
+        <v>0</v>
       </c>
       <c r="W148" s="19">
-        <v>-19355.71</v>
+        <v>-9108.58</v>
       </c>
       <c r="X148" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
     </row>
     <row r="149" spans="2:24" x14ac:dyDescent="0.35">
@@ -23806,7 +26102,7 @@
         <v>-25894.1</v>
       </c>
       <c r="X149" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="150" spans="2:24" x14ac:dyDescent="0.35">
@@ -23877,7 +26173,7 @@
         <v>-4547.18</v>
       </c>
       <c r="X150" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="151" spans="2:24" x14ac:dyDescent="0.35">
@@ -23948,7 +26244,7 @@
         <v>-2445</v>
       </c>
       <c r="X151" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="152" spans="2:24" x14ac:dyDescent="0.35">
@@ -24019,7 +26315,7 @@
         <v>-45312.568578584345</v>
       </c>
       <c r="X152" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="153" spans="2:24" x14ac:dyDescent="0.35">
@@ -24090,7 +26386,7 @@
         <v>-10051.580000000002</v>
       </c>
       <c r="X153" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="154" spans="2:24" x14ac:dyDescent="0.35">
@@ -24161,7 +26457,7 @@
         <v>-8186.04</v>
       </c>
       <c r="X154" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="155" spans="2:24" x14ac:dyDescent="0.35">
@@ -24232,7 +26528,7 @@
         <v>-10162.67</v>
       </c>
       <c r="X155" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="2:24" x14ac:dyDescent="0.35">
@@ -24303,7 +26599,7 @@
         <v>-1278</v>
       </c>
       <c r="X156" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="157" spans="2:24" x14ac:dyDescent="0.35">
@@ -24374,7 +26670,7 @@
         <v>-11379.82</v>
       </c>
       <c r="X157" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="158" spans="2:24" x14ac:dyDescent="0.35">
@@ -24445,7 +26741,7 @@
         <v>-2302.9</v>
       </c>
       <c r="X158" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="159" spans="2:24" x14ac:dyDescent="0.35">
@@ -24516,7 +26812,7 @@
         <v>-824.88000000000011</v>
       </c>
       <c r="X159" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.35">
@@ -24587,7 +26883,7 @@
         <v>-6588.880000000001</v>
       </c>
       <c r="X160" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="161" spans="2:24" x14ac:dyDescent="0.35">
@@ -24658,7 +26954,7 @@
         <v>-576</v>
       </c>
       <c r="X161" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="162" spans="2:24" x14ac:dyDescent="0.35">
@@ -24729,7 +27025,7 @@
         <v>-33169.716671709059</v>
       </c>
       <c r="X162" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="163" spans="2:24" x14ac:dyDescent="0.35">
@@ -24800,7 +27096,7 @@
         <v>-6414.57</v>
       </c>
       <c r="X163" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="164" spans="2:24" x14ac:dyDescent="0.35">
@@ -24871,7 +27167,7 @@
         <v>-450</v>
       </c>
       <c r="X164" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="165" spans="2:24" x14ac:dyDescent="0.35">
@@ -24942,7 +27238,7 @@
         <v>-8195.2999999999993</v>
       </c>
       <c r="X165" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="166" spans="2:24" x14ac:dyDescent="0.35">
@@ -25013,7 +27309,7 @@
         <v>-2065.5699999999997</v>
       </c>
       <c r="X166" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="167" spans="2:24" x14ac:dyDescent="0.35">
@@ -25084,7 +27380,7 @@
         <v>-15913.81</v>
       </c>
       <c r="X167" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="168" spans="2:24" x14ac:dyDescent="0.35">
@@ -25155,7 +27451,7 @@
         <v>-12924.32</v>
       </c>
       <c r="X168" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="169" spans="2:24" x14ac:dyDescent="0.35">
@@ -25226,7 +27522,7 @@
         <v>-1843.8000000000002</v>
       </c>
       <c r="X169" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="170" spans="2:24" x14ac:dyDescent="0.35">
@@ -25297,7 +27593,7 @@
         <v>-941.05000000000007</v>
       </c>
       <c r="X170" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="171" spans="2:24" x14ac:dyDescent="0.35">
@@ -25353,7 +27649,7 @@
         <v>-2500.1499999999996</v>
       </c>
       <c r="X171" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="172" spans="2:24" x14ac:dyDescent="0.35">
@@ -25424,7 +27720,7 @@
         <v>-36641.949999999997</v>
       </c>
       <c r="X172" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173" spans="2:24" x14ac:dyDescent="0.35">
@@ -25495,7 +27791,7 @@
         <v>-26473.21</v>
       </c>
       <c r="X173" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="174" spans="2:24" x14ac:dyDescent="0.35">
@@ -25566,7 +27862,7 @@
         <v>-13109.420000000004</v>
       </c>
       <c r="X174" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="175" spans="2:24" x14ac:dyDescent="0.35">
@@ -25637,7 +27933,7 @@
         <v>-9600.52</v>
       </c>
       <c r="X175" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="176" spans="2:24" x14ac:dyDescent="0.35">
@@ -25708,7 +28004,7 @@
         <v>-5074.0700000000006</v>
       </c>
       <c r="X176" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="177" spans="2:24" x14ac:dyDescent="0.35">
@@ -25779,7 +28075,7 @@
         <v>-1821.9600000000003</v>
       </c>
       <c r="X177" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="178" spans="2:24" x14ac:dyDescent="0.35">
@@ -25850,7 +28146,7 @@
         <v>-728.38999999999987</v>
       </c>
       <c r="X178" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="179" spans="2:24" x14ac:dyDescent="0.35">
@@ -25906,7 +28202,7 @@
         <v>-705.69999999999993</v>
       </c>
       <c r="X179" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="180" spans="2:24" x14ac:dyDescent="0.35">
@@ -25977,7 +28273,7 @@
         <v>-936.36999999999989</v>
       </c>
       <c r="X180" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="181" spans="2:24" x14ac:dyDescent="0.35">
@@ -26025,22 +28321,22 @@
         <v>0</v>
       </c>
       <c r="S181" s="19">
+        <v>0</v>
+      </c>
+      <c r="T181" s="19">
+        <v>0</v>
+      </c>
+      <c r="U181" s="19">
+        <v>0</v>
+      </c>
+      <c r="V181" s="19">
+        <v>0</v>
+      </c>
+      <c r="W181" s="19">
         <v>-581.49</v>
       </c>
-      <c r="T181" s="19">
-        <v>-581.49</v>
-      </c>
-      <c r="U181" s="19">
-        <v>-581.49</v>
-      </c>
-      <c r="V181" s="19">
-        <v>-581.49</v>
-      </c>
-      <c r="W181" s="19">
-        <v>-2907.45</v>
-      </c>
       <c r="X181" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
     </row>
     <row r="182" spans="2:24" x14ac:dyDescent="0.35">
@@ -26081,22 +28377,22 @@
         <v>-7396.59</v>
       </c>
       <c r="S182" s="19">
+        <v>0</v>
+      </c>
+      <c r="T182" s="19">
+        <v>0</v>
+      </c>
+      <c r="U182" s="19">
+        <v>0</v>
+      </c>
+      <c r="V182" s="19">
+        <v>0</v>
+      </c>
+      <c r="W182" s="19">
         <v>-7396.59</v>
       </c>
-      <c r="T182" s="19">
-        <v>-7396.59</v>
-      </c>
-      <c r="U182" s="19">
-        <v>-7396.59</v>
-      </c>
-      <c r="V182" s="19">
-        <v>-7396.59</v>
-      </c>
-      <c r="W182" s="19">
-        <v>-36982.949999999997</v>
-      </c>
       <c r="X182" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
     </row>
     <row r="183" spans="2:24" x14ac:dyDescent="0.35">
@@ -26167,7 +28463,7 @@
         <v>-30814.22</v>
       </c>
       <c r="X183" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="184" spans="2:24" x14ac:dyDescent="0.35">
@@ -26223,22 +28519,22 @@
         <v>0</v>
       </c>
       <c r="S184" s="19">
-        <v>-691.02</v>
+        <v>0</v>
       </c>
       <c r="T184" s="19">
-        <v>-691.02</v>
+        <v>0</v>
       </c>
       <c r="U184" s="19">
-        <v>-691.02</v>
+        <v>0</v>
       </c>
       <c r="V184" s="19">
-        <v>-691.02</v>
+        <v>0</v>
       </c>
       <c r="W184" s="19">
-        <v>-5528.16</v>
+        <v>-2764.08</v>
       </c>
       <c r="X184" t="s">
-        <v>456</v>
+        <v>499</v>
       </c>
     </row>
     <row r="185" spans="2:24" x14ac:dyDescent="0.35">
@@ -26283,22 +28579,22 @@
         <v>0</v>
       </c>
       <c r="S185" s="19">
+        <v>0</v>
+      </c>
+      <c r="T185" s="19">
+        <v>0</v>
+      </c>
+      <c r="U185" s="19">
+        <v>0</v>
+      </c>
+      <c r="V185" s="19">
+        <v>0</v>
+      </c>
+      <c r="W185" s="19">
         <v>-211.6</v>
       </c>
-      <c r="T185" s="19">
-        <v>-211.6</v>
-      </c>
-      <c r="U185" s="19">
-        <v>-211.6</v>
-      </c>
-      <c r="V185" s="19">
-        <v>-211.6</v>
-      </c>
-      <c r="W185" s="19">
-        <v>-1058</v>
-      </c>
       <c r="X185" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
     </row>
     <row r="186" spans="2:24" x14ac:dyDescent="0.35">
@@ -26369,7 +28665,7 @@
         <v>-37852.19999999999</v>
       </c>
       <c r="X186" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="187" spans="2:24" x14ac:dyDescent="0.35">
@@ -26440,7 +28736,7 @@
         <v>-70002.399999999994</v>
       </c>
       <c r="X187" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="188" spans="2:24" x14ac:dyDescent="0.35">
@@ -26511,7 +28807,7 @@
         <v>-76917.38</v>
       </c>
       <c r="X188" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="189" spans="2:24" x14ac:dyDescent="0.35">
@@ -26582,7 +28878,7 @@
         <v>-19096.04</v>
       </c>
       <c r="X189" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="190" spans="2:24" x14ac:dyDescent="0.35">
@@ -26653,7 +28949,7 @@
         <v>-15987.78</v>
       </c>
       <c r="X190" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="191" spans="2:24" x14ac:dyDescent="0.35">
@@ -26724,7 +29020,7 @@
         <v>-9308.9500000000007</v>
       </c>
       <c r="X191" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="192" spans="2:24" x14ac:dyDescent="0.35">
@@ -26795,7 +29091,7 @@
         <v>-510</v>
       </c>
       <c r="X192" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="193" spans="2:24" x14ac:dyDescent="0.35">
@@ -26866,7 +29162,7 @@
         <v>-299286.05000000005</v>
       </c>
       <c r="X193" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="194" spans="2:24" x14ac:dyDescent="0.35">
@@ -26925,19 +29221,19 @@
         <v>0</v>
       </c>
       <c r="T194" s="19">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="U194" s="19">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="V194" s="19">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="W194" s="19">
-        <v>-3237.05</v>
+        <v>-937.05</v>
       </c>
       <c r="X194" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
     </row>
     <row r="195" spans="2:24" x14ac:dyDescent="0.35">
@@ -26993,22 +29289,22 @@
         <v>0</v>
       </c>
       <c r="S195" s="19">
-        <v>-37.049999999999997</v>
+        <v>0</v>
       </c>
       <c r="T195" s="19">
-        <v>-37.049999999999997</v>
+        <v>0</v>
       </c>
       <c r="U195" s="19">
-        <v>-37.049999999999997</v>
+        <v>0</v>
       </c>
       <c r="V195" s="19">
-        <v>-37.049999999999997</v>
+        <v>0</v>
       </c>
       <c r="W195" s="19">
-        <v>-333.45000000000005</v>
+        <v>-185.25</v>
       </c>
       <c r="X195" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
     </row>
     <row r="196" spans="2:24" x14ac:dyDescent="0.35">
@@ -27561,22 +29857,22 @@
         <v>0</v>
       </c>
       <c r="S203" s="19">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T203" s="19">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="U203" s="19">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="V203" s="19">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="W203" s="19">
-        <v>7844.51</v>
+        <v>5244.51</v>
       </c>
       <c r="X203" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
     </row>
     <row r="204" spans="2:24" x14ac:dyDescent="0.35">
@@ -27693,13 +29989,13 @@
         <v>0</v>
       </c>
       <c r="V205" s="19">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W205" s="19">
-        <v>6995.93</v>
+        <v>4495.93</v>
       </c>
       <c r="X205" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
     </row>
     <row r="206" spans="2:24" x14ac:dyDescent="0.35">
